--- a/pds_admin_Punjab_R/Backend/Backend/Result_Sheet12_F1.xlsx
+++ b/pds_admin_Punjab_R/Backend/Backend/Result_Sheet12_F1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1256" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1186" uniqueCount="151">
   <si>
     <t>Scenario</t>
   </si>
@@ -97,412 +97,373 @@
     <t>Haryana</t>
   </si>
   <si>
-    <t>Punjab</t>
+    <t>AMRITSAR</t>
+  </si>
+  <si>
+    <t>FAZILKA</t>
   </si>
   <si>
     <t>JALANDHAR</t>
   </si>
   <si>
-    <t>FAZILKA</t>
+    <t>SRI MUKTSAR SAHIB</t>
+  </si>
+  <si>
+    <t>TARN TARAN</t>
+  </si>
+  <si>
+    <t>Stor</t>
+  </si>
+  <si>
+    <t>CHAK SAKANDAR GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>BHILOWAL GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>ABOHAR GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>BAHADUR KHERA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>BAHAAW WALA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>BUKENWALA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>BALLUANA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>BHAAGU GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>CHANNAN KHERA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>CHURHI WALA DHANNA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>DEEWAN KHERA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>DHABA KOKARIYA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>DHARANGWALA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>DHINGANWALI GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>DODHEWALA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>DUTARANWALI GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>GHALLU GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>GOBINDGARH GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>JANDWALA MEERA SANGLA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>JHUMIYANWALI GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>JHURAD KHERA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>KHUPAYA SARWAR GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>KULAR GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>KUNDAL GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>MALOOKPURA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>MAUJGARH GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>NIHAL KHERA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>PANJKOSI GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>PATRE WALA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>RUKANPURA KHUI KHERA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>SAIDANWALA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>WAREYAM KHERA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>Bhadoo Waxing Plant</t>
+  </si>
+  <si>
+    <t>P.S. Waxing Plant</t>
+  </si>
+  <si>
+    <t>Sandhu waxing plant</t>
+  </si>
+  <si>
+    <t>Sri Ram cotton &amp; oil mill</t>
+  </si>
+  <si>
+    <t>Near Mandir</t>
+  </si>
+  <si>
+    <t>Near Gurdwara Sahib</t>
+  </si>
+  <si>
+    <t>Dera Jhangi wala</t>
+  </si>
+  <si>
+    <t>Near Jandwala Meera Sangla purchase center</t>
+  </si>
+  <si>
+    <t>GHARHIANA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>MAMMU KHERA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>MURADWALA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>KUHADIANWALI GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>KHIUWALA DHAB GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>RAMKOT GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>KANDHWALA HAZARKHAN GRAIN MARKET</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADAMPUR  </t>
+  </si>
+  <si>
+    <t>BHAGSAR GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>MAHABADAR GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>sri muktsar sahib grain market</t>
+  </si>
+  <si>
+    <t>KARAM PATTI GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>KHALRA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>Depot</t>
+  </si>
+  <si>
+    <t>agah</t>
   </si>
   <si>
     <t>MALERKOTLA</t>
   </si>
   <si>
-    <t>SRI MUKTSAR SAHIB</t>
-  </si>
-  <si>
-    <t>ADAMPUR</t>
-  </si>
-  <si>
-    <t>Abohar</t>
-  </si>
-  <si>
-    <t>AHMEDGARH</t>
-  </si>
-  <si>
-    <t>Malout</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADAMPUR  </t>
-  </si>
-  <si>
-    <t>ABOHAR GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>BAHADUR KHERA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>BAHAAW WALA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>BUKENWALA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>BALLUANA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>BHAAGU GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>CHANNAN KHERA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>CHURHI WALA DHANNA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>DEEWAN KHERA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>DHABA KOKARIYA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>DHARANGWALA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>DHINGANWALI GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>DODHEWALA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>DUTARANWALI GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>GADA DOB GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>GHALLU GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>GOBINDGARH GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>JANDWALA MEERA SANGLA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>JHUMIYANWALI GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>JHURAD KHERA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>KALAR KHERA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>KHUMBAN GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>KHUPAYA SARWAR GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>KULAR GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>KUNDAL GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>MALOOKPURA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>MAUJGARH GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>NARAINPURA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>NIHAL KHERA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>PANJKOSI GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>PATRE WALA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>RUKANPURA KHUI KHERA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>SAIDANWALA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>SITO GUNO GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>VAJIDPUR BHOMA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>WAREYAM KHERA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>Bhadoo Waxing Plant</t>
-  </si>
-  <si>
-    <t>P.S. Waxing Plant</t>
-  </si>
-  <si>
-    <t>Sandhu waxing plant</t>
-  </si>
-  <si>
-    <t>Sri Ram cotton &amp; oil mill</t>
-  </si>
-  <si>
-    <t>Near Mandir</t>
-  </si>
-  <si>
-    <t>Near Gurdwara Sahib</t>
-  </si>
-  <si>
-    <t>Dera Jhangi wala</t>
-  </si>
-  <si>
-    <t>Near Jandwala Meera Sangla purchase center</t>
-  </si>
-  <si>
-    <t>GHARHIANA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>MAMMU KHERA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>MURADWALA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>KUHADIANWALI GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>BHIKHAMPUR BEGOWAL</t>
-  </si>
-  <si>
-    <t>DHALER KHURD</t>
-  </si>
-  <si>
-    <t>KANGANWAL</t>
-  </si>
-  <si>
-    <t>KUP</t>
-  </si>
-  <si>
-    <t>MAHOLI KALAN</t>
-  </si>
-  <si>
-    <t>MANAK HERI</t>
-  </si>
-  <si>
-    <t>MOMNA BAD</t>
-  </si>
-  <si>
-    <t>UMARPURA (NATHUMAJRA)</t>
-  </si>
-  <si>
-    <t>KARAM PATTI GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>Depot</t>
-  </si>
-  <si>
-    <t>agah</t>
-  </si>
-  <si>
     <t>Paddy</t>
   </si>
   <si>
+    <t>393_3</t>
+  </si>
+  <si>
+    <t>4_23</t>
+  </si>
+  <si>
+    <t>280_501</t>
+  </si>
+  <si>
+    <t>286_501</t>
+  </si>
+  <si>
+    <t>287_501</t>
+  </si>
+  <si>
+    <t>281_502</t>
+  </si>
+  <si>
+    <t>282_502</t>
+  </si>
+  <si>
+    <t>283_503</t>
+  </si>
+  <si>
+    <t>287_505</t>
+  </si>
+  <si>
+    <t>287_506</t>
+  </si>
+  <si>
+    <t>281_507</t>
+  </si>
+  <si>
+    <t>284_508</t>
+  </si>
+  <si>
+    <t>287_508</t>
+  </si>
+  <si>
+    <t>285_509</t>
+  </si>
+  <si>
+    <t>287_510</t>
+  </si>
+  <si>
+    <t>282_511</t>
+  </si>
+  <si>
+    <t>279_512</t>
+  </si>
+  <si>
+    <t>287_513</t>
+  </si>
+  <si>
+    <t>281_514</t>
+  </si>
+  <si>
+    <t>281_515</t>
+  </si>
+  <si>
+    <t>285_517</t>
+  </si>
+  <si>
+    <t>284_518</t>
+  </si>
+  <si>
+    <t>287_520</t>
+  </si>
+  <si>
+    <t>285_521</t>
+  </si>
+  <si>
+    <t>283_522</t>
+  </si>
+  <si>
+    <t>287_522</t>
+  </si>
+  <si>
+    <t>287_525</t>
+  </si>
+  <si>
+    <t>281_526</t>
+  </si>
+  <si>
+    <t>284_527</t>
+  </si>
+  <si>
+    <t>279_527</t>
+  </si>
+  <si>
+    <t>282_528</t>
+  </si>
+  <si>
+    <t>287_528</t>
+  </si>
+  <si>
+    <t>287_529</t>
+  </si>
+  <si>
+    <t>285_531</t>
+  </si>
+  <si>
+    <t>287_532</t>
+  </si>
+  <si>
+    <t>287_533</t>
+  </si>
+  <si>
+    <t>287_534</t>
+  </si>
+  <si>
+    <t>287_535</t>
+  </si>
+  <si>
+    <t>287_538</t>
+  </si>
+  <si>
+    <t>283_540</t>
+  </si>
+  <si>
+    <t>285_541</t>
+  </si>
+  <si>
+    <t>285_542</t>
+  </si>
+  <si>
+    <t>285_543</t>
+  </si>
+  <si>
+    <t>283_545</t>
+  </si>
+  <si>
+    <t>287_546</t>
+  </si>
+  <si>
+    <t>287_547</t>
+  </si>
+  <si>
+    <t>287_548</t>
+  </si>
+  <si>
+    <t>279_549</t>
+  </si>
+  <si>
+    <t>285_550</t>
+  </si>
+  <si>
+    <t>279_551</t>
+  </si>
+  <si>
+    <t>279_552</t>
+  </si>
+  <si>
+    <t>285_560</t>
+  </si>
+  <si>
+    <t>285_565</t>
+  </si>
+  <si>
+    <t>279_612</t>
+  </si>
+  <si>
     <t>522_1046</t>
   </si>
   <si>
-    <t>280_501</t>
-  </si>
-  <si>
-    <t>286_501</t>
-  </si>
-  <si>
-    <t>284_501</t>
-  </si>
-  <si>
-    <t>287_502</t>
-  </si>
-  <si>
-    <t>283_503</t>
-  </si>
-  <si>
-    <t>287_503</t>
-  </si>
-  <si>
-    <t>287_505</t>
-  </si>
-  <si>
-    <t>284_506</t>
-  </si>
-  <si>
-    <t>281_507</t>
-  </si>
-  <si>
-    <t>284_508</t>
-  </si>
-  <si>
-    <t>285_509</t>
-  </si>
-  <si>
-    <t>287_510</t>
-  </si>
-  <si>
-    <t>287_511</t>
-  </si>
-  <si>
-    <t>279_512</t>
-  </si>
-  <si>
-    <t>287_513</t>
-  </si>
-  <si>
-    <t>283_514</t>
-  </si>
-  <si>
-    <t>282_515</t>
-  </si>
-  <si>
-    <t>287_515</t>
-  </si>
-  <si>
-    <t>279_516</t>
-  </si>
-  <si>
-    <t>284_516</t>
-  </si>
-  <si>
-    <t>285_517</t>
-  </si>
-  <si>
-    <t>284_518</t>
-  </si>
-  <si>
-    <t>285_520</t>
-  </si>
-  <si>
-    <t>287_520</t>
-  </si>
-  <si>
-    <t>279_521</t>
-  </si>
-  <si>
-    <t>285_521</t>
-  </si>
-  <si>
-    <t>287_522</t>
-  </si>
-  <si>
-    <t>287_523</t>
-  </si>
-  <si>
-    <t>281_524</t>
-  </si>
-  <si>
-    <t>287_525</t>
-  </si>
-  <si>
-    <t>281_526</t>
-  </si>
-  <si>
-    <t>279_527</t>
-  </si>
-  <si>
-    <t>287_528</t>
-  </si>
-  <si>
-    <t>287_529</t>
-  </si>
-  <si>
-    <t>281_530</t>
-  </si>
-  <si>
-    <t>285_531</t>
-  </si>
-  <si>
-    <t>287_532</t>
-  </si>
-  <si>
-    <t>287_533</t>
-  </si>
-  <si>
-    <t>287_534</t>
-  </si>
-  <si>
-    <t>287_535</t>
-  </si>
-  <si>
-    <t>281_536</t>
-  </si>
-  <si>
-    <t>281_537</t>
-  </si>
-  <si>
-    <t>287_538</t>
-  </si>
-  <si>
-    <t>287_540</t>
-  </si>
-  <si>
-    <t>285_541</t>
-  </si>
-  <si>
-    <t>285_542</t>
-  </si>
-  <si>
-    <t>285_543</t>
-  </si>
-  <si>
-    <t>287_545</t>
-  </si>
-  <si>
-    <t>287_546</t>
-  </si>
-  <si>
-    <t>287_547</t>
-  </si>
-  <si>
-    <t>285_548</t>
-  </si>
-  <si>
-    <t>279_549</t>
-  </si>
-  <si>
-    <t>285_550</t>
-  </si>
-  <si>
-    <t>279_551</t>
-  </si>
-  <si>
-    <t>279_552</t>
-  </si>
-  <si>
-    <t>703_1322</t>
-  </si>
-  <si>
-    <t>999_1323</t>
-  </si>
-  <si>
-    <t>216_1324</t>
-  </si>
-  <si>
-    <t>217_1325</t>
-  </si>
-  <si>
-    <t>57_1326</t>
-  </si>
-  <si>
-    <t>217_1327</t>
-  </si>
-  <si>
-    <t>216_1328</t>
-  </si>
-  <si>
-    <t>678_1329</t>
-  </si>
-  <si>
-    <t>1225_1330</t>
-  </si>
-  <si>
-    <t>287_1660</t>
+    <t>1455_1577</t>
+  </si>
+  <si>
+    <t>1455_1597</t>
+  </si>
+  <si>
+    <t>1512_1607</t>
+  </si>
+  <si>
+    <t>279_1660</t>
+  </si>
+  <si>
+    <t>1948_2153</t>
   </si>
   <si>
     <t>shallu</t>
@@ -863,7 +824,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:X89"/>
+  <dimension ref="A1:X84"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:24">
@@ -951,67 +912,67 @@
         <v>26</v>
       </c>
       <c r="D2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E2" t="s">
         <v>32</v>
       </c>
       <c r="F2">
-        <v>1046</v>
+        <v>3</v>
       </c>
       <c r="G2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="H2">
-        <v>31.425406</v>
+        <v>31.84430551</v>
       </c>
       <c r="I2">
-        <v>75.719528</v>
+        <v>74.91208039999999</v>
       </c>
       <c r="J2">
-        <v>522</v>
+        <v>393</v>
       </c>
       <c r="K2">
-        <v>31.4204409</v>
+        <v>31.863261</v>
       </c>
       <c r="L2">
-        <v>75.69994199999999</v>
+        <v>74.945286</v>
       </c>
       <c r="M2" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="N2">
-        <v>625</v>
+        <v>3</v>
       </c>
       <c r="O2" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P2" t="s">
         <v>26</v>
       </c>
       <c r="Q2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R2" t="s">
         <v>32</v>
       </c>
       <c r="S2">
-        <v>31.408658</v>
+        <v>31.8529346</v>
       </c>
       <c r="T2">
-        <v>75.685958</v>
+        <v>74.91584450000001</v>
       </c>
       <c r="U2" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="V2">
-        <v>21500</v>
+        <v>50000</v>
       </c>
       <c r="W2" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="X2" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
     </row>
     <row r="3" spans="1:24">
@@ -1025,67 +986,67 @@
         <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F3">
-        <v>501</v>
+        <v>23</v>
       </c>
       <c r="G3" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="H3">
-        <v>30.156605</v>
+        <v>31.7398221</v>
       </c>
       <c r="I3">
-        <v>74.19572100000001</v>
+        <v>74.6072853</v>
       </c>
       <c r="J3">
-        <v>280</v>
+        <v>4</v>
       </c>
       <c r="K3">
-        <v>30.154922</v>
+        <v>31.781936</v>
       </c>
       <c r="L3">
-        <v>74.193507</v>
+        <v>74.76758049999999</v>
       </c>
       <c r="M3" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="N3">
-        <v>396</v>
+        <v>5</v>
       </c>
       <c r="O3" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P3" t="s">
         <v>26</v>
       </c>
       <c r="Q3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="R3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S3">
-        <v>30.15881226</v>
+        <v>31.800077</v>
       </c>
       <c r="T3">
-        <v>74.18214294000001</v>
+        <v>74.588493</v>
       </c>
       <c r="U3" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="V3">
-        <v>90000</v>
+        <v>50000</v>
       </c>
       <c r="W3" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="X3" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
     </row>
     <row r="4" spans="1:24">
@@ -1099,16 +1060,16 @@
         <v>26</v>
       </c>
       <c r="D4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F4">
         <v>501</v>
       </c>
       <c r="G4" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H4">
         <v>30.156605</v>
@@ -1117,49 +1078,49 @@
         <v>74.19572100000001</v>
       </c>
       <c r="J4">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="K4">
-        <v>30.15894356</v>
+        <v>30.154922</v>
       </c>
       <c r="L4">
-        <v>74.18094151</v>
+        <v>74.193507</v>
       </c>
       <c r="M4" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="N4">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="O4" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P4" t="s">
         <v>26</v>
       </c>
       <c r="Q4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S4">
-        <v>30.15894356</v>
+        <v>30.15881226</v>
       </c>
       <c r="T4">
-        <v>74.18094151</v>
+        <v>74.18214294000001</v>
       </c>
       <c r="U4" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="V4">
-        <v>60000</v>
+        <v>90000</v>
       </c>
       <c r="W4" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="X4" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
     </row>
     <row r="5" spans="1:24">
@@ -1173,16 +1134,16 @@
         <v>26</v>
       </c>
       <c r="D5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F5">
         <v>501</v>
       </c>
       <c r="G5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H5">
         <v>30.156605</v>
@@ -1200,40 +1161,40 @@
         <v>74.18094151</v>
       </c>
       <c r="M5" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="N5">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="O5" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P5" t="s">
         <v>26</v>
       </c>
       <c r="Q5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S5">
-        <v>30.15848535</v>
+        <v>30.15894356</v>
       </c>
       <c r="T5">
-        <v>74.18085842000001</v>
+        <v>74.18094151</v>
       </c>
       <c r="U5" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="V5">
-        <v>120000</v>
+        <v>60000</v>
       </c>
       <c r="W5" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="X5" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6" spans="1:24">
@@ -1247,16 +1208,16 @@
         <v>26</v>
       </c>
       <c r="D6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F6">
         <v>501</v>
       </c>
       <c r="G6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H6">
         <v>30.156605</v>
@@ -1274,40 +1235,40 @@
         <v>74.18094151</v>
       </c>
       <c r="M6" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="N6">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="O6" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P6" t="s">
         <v>26</v>
       </c>
       <c r="Q6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S6">
-        <v>30.15809938</v>
+        <v>30.15848535</v>
       </c>
       <c r="T6">
-        <v>74.16401603</v>
+        <v>74.18085842000001</v>
       </c>
       <c r="U6" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="V6">
-        <v>145397</v>
+        <v>120000</v>
       </c>
       <c r="W6" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="X6" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
     </row>
     <row r="7" spans="1:24">
@@ -1321,16 +1282,16 @@
         <v>26</v>
       </c>
       <c r="D7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F7">
         <v>501</v>
       </c>
       <c r="G7" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H7">
         <v>30.156605</v>
@@ -1339,49 +1300,49 @@
         <v>74.19572100000001</v>
       </c>
       <c r="J7">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="K7">
-        <v>30.163017</v>
+        <v>30.15894356</v>
       </c>
       <c r="L7">
-        <v>74.186234</v>
+        <v>74.18094151</v>
       </c>
       <c r="M7" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="N7">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="O7" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P7" t="s">
         <v>26</v>
       </c>
       <c r="Q7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S7">
-        <v>30.1689126</v>
+        <v>30.15809938</v>
       </c>
       <c r="T7">
-        <v>74.183232</v>
+        <v>74.16401603</v>
       </c>
       <c r="U7" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="V7">
-        <v>31477</v>
+        <v>33610</v>
       </c>
       <c r="W7" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="X7" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
     </row>
     <row r="8" spans="1:24">
@@ -1395,16 +1356,16 @@
         <v>26</v>
       </c>
       <c r="D8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F8">
         <v>501</v>
       </c>
       <c r="G8" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H8">
         <v>30.156605</v>
@@ -1422,22 +1383,22 @@
         <v>74.193507</v>
       </c>
       <c r="M8" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="N8">
         <v>405</v>
       </c>
       <c r="O8" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P8" t="s">
         <v>26</v>
       </c>
       <c r="Q8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S8">
         <v>30.15857797</v>
@@ -1446,16 +1407,16 @@
         <v>74.18315728</v>
       </c>
       <c r="U8" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="V8">
         <v>150000</v>
       </c>
       <c r="W8" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="X8" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
     </row>
     <row r="9" spans="1:24">
@@ -1469,22 +1430,22 @@
         <v>26</v>
       </c>
       <c r="D9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F9">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="G9" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="H9">
-        <v>30.099748</v>
+        <v>30.156605</v>
       </c>
       <c r="I9">
-        <v>74.34759699999999</v>
+        <v>74.19572100000001</v>
       </c>
       <c r="J9">
         <v>287</v>
@@ -1496,22 +1457,22 @@
         <v>74.161942</v>
       </c>
       <c r="M9" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="N9">
         <v>407</v>
       </c>
       <c r="O9" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P9" t="s">
         <v>26</v>
       </c>
       <c r="Q9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S9">
         <v>30.126927</v>
@@ -1520,16 +1481,16 @@
         <v>74.161942</v>
       </c>
       <c r="U9" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="V9">
-        <v>71835.5</v>
+        <v>143264</v>
       </c>
       <c r="W9" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="X9" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
     </row>
     <row r="10" spans="1:24">
@@ -1543,67 +1504,67 @@
         <v>26</v>
       </c>
       <c r="D10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F10">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="G10" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H10">
-        <v>30.028699</v>
+        <v>30.099748</v>
       </c>
       <c r="I10">
-        <v>74.197309</v>
+        <v>74.34759699999999</v>
       </c>
       <c r="J10">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="K10">
-        <v>30.105887</v>
+        <v>30.090357</v>
       </c>
       <c r="L10">
-        <v>74.18092900000001</v>
+        <v>74.20853700000001</v>
       </c>
       <c r="M10" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="N10">
-        <v>404</v>
+        <v>394</v>
       </c>
       <c r="O10" t="s">
+        <v>87</v>
+      </c>
+      <c r="P10" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>28</v>
+      </c>
+      <c r="R10" t="s">
+        <v>32</v>
+      </c>
+      <c r="S10">
+        <v>30.08793156</v>
+      </c>
+      <c r="T10">
+        <v>74.20908439</v>
+      </c>
+      <c r="U10" t="s">
+        <v>89</v>
+      </c>
+      <c r="V10">
+        <v>48247.5</v>
+      </c>
+      <c r="W10" t="s">
         <v>95</v>
       </c>
-      <c r="P10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>29</v>
-      </c>
-      <c r="R10" t="s">
-        <v>33</v>
-      </c>
-      <c r="S10">
-        <v>30.10552983</v>
-      </c>
-      <c r="T10">
-        <v>74.18014506</v>
-      </c>
-      <c r="U10" t="s">
-        <v>96</v>
-      </c>
-      <c r="V10">
-        <v>73538.5</v>
-      </c>
-      <c r="W10" t="s">
-        <v>102</v>
-      </c>
       <c r="X10" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
     </row>
     <row r="11" spans="1:24">
@@ -1617,67 +1578,67 @@
         <v>26</v>
       </c>
       <c r="D11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F11">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="G11" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H11">
-        <v>30.028699</v>
+        <v>30.099748</v>
       </c>
       <c r="I11">
-        <v>74.197309</v>
+        <v>74.34759699999999</v>
       </c>
       <c r="J11">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="K11">
-        <v>30.126927</v>
+        <v>30.100105</v>
       </c>
       <c r="L11">
-        <v>74.161942</v>
+        <v>74.20670699999999</v>
       </c>
       <c r="M11" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="N11">
-        <v>407</v>
+        <v>397</v>
       </c>
       <c r="O11" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P11" t="s">
         <v>26</v>
       </c>
       <c r="Q11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S11">
-        <v>30.126927</v>
+        <v>30.0974593</v>
       </c>
       <c r="T11">
-        <v>74.161942</v>
+        <v>74.206666</v>
       </c>
       <c r="U11" t="s">
+        <v>89</v>
+      </c>
+      <c r="V11">
+        <v>23588</v>
+      </c>
+      <c r="W11" t="s">
         <v>96</v>
       </c>
-      <c r="V11">
-        <v>322</v>
-      </c>
-      <c r="W11" t="s">
-        <v>103</v>
-      </c>
       <c r="X11" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
     </row>
     <row r="12" spans="1:24">
@@ -1691,67 +1652,67 @@
         <v>26</v>
       </c>
       <c r="D12" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F12">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="G12" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="H12">
-        <v>30.162859</v>
+        <v>30.028699</v>
       </c>
       <c r="I12">
-        <v>73.991192</v>
+        <v>74.197309</v>
       </c>
       <c r="J12">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="K12">
-        <v>30.126927</v>
+        <v>30.105887</v>
       </c>
       <c r="L12">
-        <v>74.161942</v>
+        <v>74.18092900000001</v>
       </c>
       <c r="M12" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="N12">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="O12" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P12" t="s">
         <v>26</v>
       </c>
       <c r="Q12" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S12">
-        <v>30.126927</v>
+        <v>30.10552983</v>
       </c>
       <c r="T12">
-        <v>74.161942</v>
+        <v>74.18014506</v>
       </c>
       <c r="U12" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="V12">
-        <v>37309</v>
+        <v>73860.5</v>
       </c>
       <c r="W12" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="X12" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
     </row>
     <row r="13" spans="1:24">
@@ -1765,67 +1726,67 @@
         <v>26</v>
       </c>
       <c r="D13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F13">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="G13" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="H13">
-        <v>30.16948</v>
+        <v>30.162859</v>
       </c>
       <c r="I13">
-        <v>74.28432100000001</v>
+        <v>73.991192</v>
       </c>
       <c r="J13">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="K13">
-        <v>30.163017</v>
+        <v>30.126927</v>
       </c>
       <c r="L13">
-        <v>74.186234</v>
+        <v>74.161942</v>
       </c>
       <c r="M13" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="N13">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="O13" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P13" t="s">
         <v>26</v>
       </c>
       <c r="Q13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S13">
-        <v>30.1689126</v>
+        <v>30.126927</v>
       </c>
       <c r="T13">
-        <v>74.183232</v>
+        <v>74.161942</v>
       </c>
       <c r="U13" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="V13">
-        <v>2823</v>
+        <v>37309</v>
       </c>
       <c r="W13" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="X13" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
     </row>
     <row r="14" spans="1:24">
@@ -1839,16 +1800,16 @@
         <v>26</v>
       </c>
       <c r="D14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F14">
         <v>506</v>
       </c>
       <c r="G14" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H14">
         <v>30.16948</v>
@@ -1857,49 +1818,49 @@
         <v>74.28432100000001</v>
       </c>
       <c r="J14">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="K14">
-        <v>30.163017</v>
+        <v>30.126927</v>
       </c>
       <c r="L14">
-        <v>74.186234</v>
+        <v>74.161942</v>
       </c>
       <c r="M14" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="N14">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="O14" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P14" t="s">
         <v>26</v>
       </c>
       <c r="Q14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S14">
-        <v>30.16991135</v>
+        <v>30.126927</v>
       </c>
       <c r="T14">
-        <v>74.18230296</v>
+        <v>74.161942</v>
       </c>
       <c r="U14" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="V14">
-        <v>15202.5</v>
+        <v>18025.5</v>
       </c>
       <c r="W14" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="X14" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
     </row>
     <row r="15" spans="1:24">
@@ -1913,16 +1874,16 @@
         <v>26</v>
       </c>
       <c r="D15" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F15">
         <v>507</v>
       </c>
       <c r="G15" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H15">
         <v>30.034436</v>
@@ -1940,40 +1901,40 @@
         <v>74.20853700000001</v>
       </c>
       <c r="M15" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="N15">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="O15" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P15" t="s">
         <v>26</v>
       </c>
       <c r="Q15" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S15">
-        <v>30.08675444</v>
+        <v>30.08793156</v>
       </c>
       <c r="T15">
-        <v>74.20888524</v>
+        <v>74.20908439</v>
       </c>
       <c r="U15" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="V15">
-        <v>49766</v>
+        <v>16177.5</v>
       </c>
       <c r="W15" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="X15" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
     </row>
     <row r="16" spans="1:24">
@@ -1987,67 +1948,67 @@
         <v>26</v>
       </c>
       <c r="D16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E16" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F16">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="G16" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="H16">
-        <v>30.182524</v>
+        <v>30.034436</v>
       </c>
       <c r="I16">
-        <v>74.326095</v>
+        <v>74.233859</v>
       </c>
       <c r="J16">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="K16">
-        <v>30.163017</v>
+        <v>30.090357</v>
       </c>
       <c r="L16">
-        <v>74.186234</v>
+        <v>74.20853700000001</v>
       </c>
       <c r="M16" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="N16">
-        <v>406</v>
+        <v>395</v>
       </c>
       <c r="O16" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P16" t="s">
         <v>26</v>
       </c>
       <c r="Q16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R16" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S16">
-        <v>30.16991135</v>
+        <v>30.08675444</v>
       </c>
       <c r="T16">
-        <v>74.18230296</v>
+        <v>74.20888524</v>
       </c>
       <c r="U16" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="V16">
-        <v>41707.5</v>
+        <v>33588.5</v>
       </c>
       <c r="W16" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="X16" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
     </row>
     <row r="17" spans="1:24">
@@ -2061,67 +2022,67 @@
         <v>26</v>
       </c>
       <c r="D17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E17" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F17">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="G17" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="H17">
-        <v>30.199756</v>
+        <v>30.182524</v>
       </c>
       <c r="I17">
-        <v>74.108656</v>
+        <v>74.326095</v>
       </c>
       <c r="J17">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="K17">
-        <v>30.180346</v>
+        <v>30.163017</v>
       </c>
       <c r="L17">
-        <v>74.17439299999999</v>
+        <v>74.186234</v>
       </c>
       <c r="M17" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="N17">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="O17" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P17" t="s">
         <v>26</v>
       </c>
       <c r="Q17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R17" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S17">
-        <v>30.15809938</v>
+        <v>30.1689126</v>
       </c>
       <c r="T17">
-        <v>74.16401603</v>
+        <v>74.183232</v>
       </c>
       <c r="U17" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="V17">
-        <v>18038</v>
+        <v>13129</v>
       </c>
       <c r="W17" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="X17" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
     </row>
     <row r="18" spans="1:24">
@@ -2135,22 +2096,22 @@
         <v>26</v>
       </c>
       <c r="D18" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E18" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F18">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="G18" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="H18">
-        <v>30.113508</v>
+        <v>30.182524</v>
       </c>
       <c r="I18">
-        <v>73.989543</v>
+        <v>74.326095</v>
       </c>
       <c r="J18">
         <v>287</v>
@@ -2162,22 +2123,22 @@
         <v>74.161942</v>
       </c>
       <c r="M18" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="N18">
         <v>407</v>
       </c>
       <c r="O18" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P18" t="s">
         <v>26</v>
       </c>
       <c r="Q18" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R18" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S18">
         <v>30.126927</v>
@@ -2186,16 +2147,16 @@
         <v>74.161942</v>
       </c>
       <c r="U18" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="V18">
-        <v>44568.5</v>
+        <v>28578.5</v>
       </c>
       <c r="W18" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="X18" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
     </row>
     <row r="19" spans="1:24">
@@ -2209,67 +2170,67 @@
         <v>26</v>
       </c>
       <c r="D19" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E19" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F19">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="G19" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="H19">
-        <v>30.122605</v>
+        <v>30.199756</v>
       </c>
       <c r="I19">
-        <v>74.328892</v>
+        <v>74.108656</v>
       </c>
       <c r="J19">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="K19">
-        <v>30.126927</v>
+        <v>30.180346</v>
       </c>
       <c r="L19">
-        <v>74.161942</v>
+        <v>74.17439299999999</v>
       </c>
       <c r="M19" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="N19">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="O19" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P19" t="s">
         <v>26</v>
       </c>
       <c r="Q19" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R19" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S19">
-        <v>30.126927</v>
+        <v>30.15809938</v>
       </c>
       <c r="T19">
-        <v>74.161942</v>
+        <v>74.16401603</v>
       </c>
       <c r="U19" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="V19">
-        <v>25216</v>
+        <v>18038</v>
       </c>
       <c r="W19" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="X19" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
     </row>
     <row r="20" spans="1:24">
@@ -2283,67 +2244,67 @@
         <v>26</v>
       </c>
       <c r="D20" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E20" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F20">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="G20" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H20">
-        <v>30.237206</v>
+        <v>30.113508</v>
       </c>
       <c r="I20">
-        <v>74.23982700000001</v>
+        <v>73.989543</v>
       </c>
       <c r="J20">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="K20">
-        <v>30.175344</v>
+        <v>30.126927</v>
       </c>
       <c r="L20">
-        <v>74.178363</v>
+        <v>74.161942</v>
       </c>
       <c r="M20" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="N20">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="O20" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P20" t="s">
         <v>26</v>
       </c>
       <c r="Q20" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R20" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S20">
-        <v>30.17081207</v>
+        <v>30.126927</v>
       </c>
       <c r="T20">
-        <v>74.18179719</v>
+        <v>74.161942</v>
       </c>
       <c r="U20" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="V20">
-        <v>44802</v>
+        <v>44568.5</v>
       </c>
       <c r="W20" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="X20" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
     </row>
     <row r="21" spans="1:24">
@@ -2357,67 +2318,67 @@
         <v>26</v>
       </c>
       <c r="D21" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E21" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F21">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="G21" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H21">
-        <v>30.023582</v>
+        <v>30.122605</v>
       </c>
       <c r="I21">
-        <v>74.04262799999999</v>
+        <v>74.328892</v>
       </c>
       <c r="J21">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="K21">
-        <v>30.126927</v>
+        <v>30.100105</v>
       </c>
       <c r="L21">
-        <v>74.161942</v>
+        <v>74.20670699999999</v>
       </c>
       <c r="M21" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="N21">
-        <v>407</v>
+        <v>397</v>
       </c>
       <c r="O21" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P21" t="s">
         <v>26</v>
       </c>
       <c r="Q21" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R21" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S21">
-        <v>30.126927</v>
+        <v>30.0974593</v>
       </c>
       <c r="T21">
-        <v>74.161942</v>
+        <v>74.206666</v>
       </c>
       <c r="U21" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="V21">
-        <v>30276.5</v>
+        <v>25216</v>
       </c>
       <c r="W21" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="X21" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
     </row>
     <row r="22" spans="1:24">
@@ -2431,67 +2392,67 @@
         <v>26</v>
       </c>
       <c r="D22" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E22" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F22">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="G22" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="H22">
-        <v>29.960526</v>
+        <v>30.237206</v>
       </c>
       <c r="I22">
-        <v>74.219824</v>
+        <v>74.23982700000001</v>
       </c>
       <c r="J22">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="K22">
-        <v>30.105887</v>
+        <v>30.175344</v>
       </c>
       <c r="L22">
-        <v>74.18092900000001</v>
+        <v>74.178363</v>
       </c>
       <c r="M22" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="N22">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="O22" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P22" t="s">
         <v>26</v>
       </c>
       <c r="Q22" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R22" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S22">
-        <v>30.10552983</v>
+        <v>30.17081207</v>
       </c>
       <c r="T22">
-        <v>74.18014506</v>
+        <v>74.18179719</v>
       </c>
       <c r="U22" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="V22">
-        <v>19961.5</v>
+        <v>44802</v>
       </c>
       <c r="W22" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="X22" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
     </row>
     <row r="23" spans="1:24">
@@ -2505,67 +2466,67 @@
         <v>26</v>
       </c>
       <c r="D23" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E23" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F23">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="G23" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H23">
-        <v>30.082625</v>
+        <v>30.023582</v>
       </c>
       <c r="I23">
-        <v>74.288794</v>
+        <v>74.04262799999999</v>
       </c>
       <c r="J23">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="K23">
-        <v>30.100105</v>
+        <v>30.126927</v>
       </c>
       <c r="L23">
-        <v>74.20670699999999</v>
+        <v>74.161942</v>
       </c>
       <c r="M23" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="N23">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O23" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P23" t="s">
         <v>26</v>
       </c>
       <c r="Q23" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R23" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S23">
-        <v>30.0974593</v>
+        <v>30.126927</v>
       </c>
       <c r="T23">
-        <v>74.206666</v>
+        <v>74.161942</v>
       </c>
       <c r="U23" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="V23">
-        <v>9709</v>
+        <v>30276.5</v>
       </c>
       <c r="W23" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="X23" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
     </row>
     <row r="24" spans="1:24">
@@ -2579,67 +2540,67 @@
         <v>26</v>
       </c>
       <c r="D24" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E24" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F24">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="G24" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="H24">
-        <v>30.082625</v>
+        <v>29.960526</v>
       </c>
       <c r="I24">
-        <v>74.288794</v>
+        <v>74.219824</v>
       </c>
       <c r="J24">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="K24">
-        <v>30.126927</v>
+        <v>30.090357</v>
       </c>
       <c r="L24">
-        <v>74.161942</v>
+        <v>74.20853700000001</v>
       </c>
       <c r="M24" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="N24">
-        <v>407</v>
+        <v>395</v>
       </c>
       <c r="O24" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P24" t="s">
         <v>26</v>
       </c>
       <c r="Q24" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R24" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S24">
-        <v>30.126927</v>
+        <v>30.08675444</v>
       </c>
       <c r="T24">
-        <v>74.161942</v>
+        <v>74.20888524</v>
       </c>
       <c r="U24" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="V24">
-        <v>54672</v>
+        <v>19961.5</v>
       </c>
       <c r="W24" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="X24" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
     </row>
     <row r="25" spans="1:24">
@@ -2653,67 +2614,67 @@
         <v>26</v>
       </c>
       <c r="D25" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E25" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F25">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="G25" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="H25">
-        <v>30.221432</v>
+        <v>30.082625</v>
       </c>
       <c r="I25">
-        <v>74.35153099999999</v>
+        <v>74.288794</v>
       </c>
       <c r="J25">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="K25">
-        <v>30.175344</v>
+        <v>30.090357</v>
       </c>
       <c r="L25">
-        <v>74.178363</v>
+        <v>74.20853700000001</v>
       </c>
       <c r="M25" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="N25">
-        <v>401</v>
+        <v>394</v>
       </c>
       <c r="O25" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P25" t="s">
         <v>26</v>
       </c>
       <c r="Q25" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R25" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S25">
-        <v>30.17081207</v>
+        <v>30.08793156</v>
       </c>
       <c r="T25">
-        <v>74.18179719</v>
+        <v>74.20908439</v>
       </c>
       <c r="U25" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="V25">
-        <v>13755.5</v>
+        <v>64381</v>
       </c>
       <c r="W25" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="X25" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
     </row>
     <row r="26" spans="1:24">
@@ -2727,67 +2688,67 @@
         <v>26</v>
       </c>
       <c r="D26" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E26" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F26">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="G26" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H26">
-        <v>30.221432</v>
+        <v>30.254598</v>
       </c>
       <c r="I26">
-        <v>74.35153099999999</v>
+        <v>74.124285</v>
       </c>
       <c r="J26">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="K26">
-        <v>30.163017</v>
+        <v>30.180346</v>
       </c>
       <c r="L26">
-        <v>74.186234</v>
+        <v>74.17439299999999</v>
       </c>
       <c r="M26" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="N26">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="O26" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P26" t="s">
         <v>26</v>
       </c>
       <c r="Q26" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R26" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S26">
-        <v>30.16991135</v>
+        <v>30.15809938</v>
       </c>
       <c r="T26">
-        <v>74.18230296</v>
+        <v>74.16401603</v>
       </c>
       <c r="U26" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="V26">
-        <v>6714.5</v>
+        <v>39817.5</v>
       </c>
       <c r="W26" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="X26" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
     </row>
     <row r="27" spans="1:24">
@@ -2801,67 +2762,67 @@
         <v>26</v>
       </c>
       <c r="D27" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E27" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F27">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="G27" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="H27">
-        <v>30.254598</v>
+        <v>30.173582</v>
       </c>
       <c r="I27">
-        <v>74.124285</v>
+        <v>74.250483</v>
       </c>
       <c r="J27">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="K27">
-        <v>30.180346</v>
+        <v>30.163017</v>
       </c>
       <c r="L27">
-        <v>74.17439299999999</v>
+        <v>74.186234</v>
       </c>
       <c r="M27" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="N27">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="O27" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P27" t="s">
         <v>26</v>
       </c>
       <c r="Q27" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R27" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S27">
-        <v>30.15809938</v>
+        <v>30.1689126</v>
       </c>
       <c r="T27">
-        <v>74.16401603</v>
+        <v>74.183232</v>
       </c>
       <c r="U27" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="V27">
-        <v>39817.5</v>
+        <v>10375.5</v>
       </c>
       <c r="W27" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="X27" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
     </row>
     <row r="28" spans="1:24">
@@ -2875,67 +2836,67 @@
         <v>26</v>
       </c>
       <c r="D28" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E28" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F28">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="G28" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H28">
-        <v>30.173582</v>
+        <v>30.21019</v>
       </c>
       <c r="I28">
-        <v>74.250483</v>
+        <v>74.024728</v>
       </c>
       <c r="J28">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="K28">
-        <v>30.163017</v>
+        <v>30.126927</v>
       </c>
       <c r="L28">
-        <v>74.186234</v>
+        <v>74.161942</v>
       </c>
       <c r="M28" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="N28">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="O28" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P28" t="s">
         <v>26</v>
       </c>
       <c r="Q28" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R28" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S28">
-        <v>30.16991135</v>
+        <v>30.126927</v>
       </c>
       <c r="T28">
-        <v>74.18230296</v>
+        <v>74.161942</v>
       </c>
       <c r="U28" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="V28">
-        <v>10375.5</v>
+        <v>100949.5</v>
       </c>
       <c r="W28" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="X28" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
     </row>
     <row r="29" spans="1:24">
@@ -2949,22 +2910,22 @@
         <v>26</v>
       </c>
       <c r="D29" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E29" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F29">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="G29" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="H29">
-        <v>30.21019</v>
+        <v>30.257887</v>
       </c>
       <c r="I29">
-        <v>74.024728</v>
+        <v>74.185624</v>
       </c>
       <c r="J29">
         <v>285</v>
@@ -2976,40 +2937,40 @@
         <v>74.17439299999999</v>
       </c>
       <c r="M29" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="N29">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="O29" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P29" t="s">
         <v>26</v>
       </c>
       <c r="Q29" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R29" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S29">
-        <v>30.15809938</v>
+        <v>30.17767461</v>
       </c>
       <c r="T29">
-        <v>74.16401603</v>
+        <v>74.17723581</v>
       </c>
       <c r="U29" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="V29">
-        <v>72343</v>
+        <v>36622.5</v>
       </c>
       <c r="W29" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="X29" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
     </row>
     <row r="30" spans="1:24">
@@ -3023,67 +2984,67 @@
         <v>26</v>
       </c>
       <c r="D30" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E30" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F30">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="G30" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H30">
-        <v>30.21019</v>
+        <v>30.007285</v>
       </c>
       <c r="I30">
-        <v>74.024728</v>
+        <v>74.126166</v>
       </c>
       <c r="J30">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="K30">
-        <v>30.126927</v>
+        <v>30.105887</v>
       </c>
       <c r="L30">
-        <v>74.161942</v>
+        <v>74.18092900000001</v>
       </c>
       <c r="M30" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="N30">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="O30" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P30" t="s">
         <v>26</v>
       </c>
       <c r="Q30" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R30" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S30">
-        <v>30.126927</v>
+        <v>30.10552983</v>
       </c>
       <c r="T30">
-        <v>74.161942</v>
+        <v>74.18014506</v>
       </c>
       <c r="U30" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="V30">
-        <v>28606.5</v>
+        <v>11652.5</v>
       </c>
       <c r="W30" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="X30" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
     </row>
     <row r="31" spans="1:24">
@@ -3097,67 +3058,67 @@
         <v>26</v>
       </c>
       <c r="D31" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E31" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F31">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="G31" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H31">
-        <v>30.257887</v>
+        <v>30.007285</v>
       </c>
       <c r="I31">
-        <v>74.185624</v>
+        <v>74.126166</v>
       </c>
       <c r="J31">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="K31">
-        <v>30.175344</v>
+        <v>30.126927</v>
       </c>
       <c r="L31">
-        <v>74.178363</v>
+        <v>74.161942</v>
       </c>
       <c r="M31" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="N31">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="O31" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P31" t="s">
         <v>26</v>
       </c>
       <c r="Q31" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R31" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S31">
-        <v>30.17081207</v>
+        <v>30.126927</v>
       </c>
       <c r="T31">
-        <v>74.18179719</v>
+        <v>74.161942</v>
       </c>
       <c r="U31" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="V31">
-        <v>2347.5</v>
+        <v>16592.5</v>
       </c>
       <c r="W31" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="X31" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
     </row>
     <row r="32" spans="1:24">
@@ -3171,67 +3132,67 @@
         <v>26</v>
       </c>
       <c r="D32" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E32" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F32">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="G32" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H32">
-        <v>30.257887</v>
+        <v>30.127701</v>
       </c>
       <c r="I32">
-        <v>74.185624</v>
+        <v>74.06368999999999</v>
       </c>
       <c r="J32">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="K32">
-        <v>30.180346</v>
+        <v>30.126927</v>
       </c>
       <c r="L32">
-        <v>74.17439299999999</v>
+        <v>74.161942</v>
       </c>
       <c r="M32" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="N32">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="O32" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P32" t="s">
         <v>26</v>
       </c>
       <c r="Q32" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R32" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S32">
-        <v>30.17767461</v>
+        <v>30.126927</v>
       </c>
       <c r="T32">
-        <v>74.17723581</v>
+        <v>74.161942</v>
       </c>
       <c r="U32" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="V32">
-        <v>34275</v>
+        <v>21311</v>
       </c>
       <c r="W32" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="X32" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
     </row>
     <row r="33" spans="1:24">
@@ -3245,67 +3206,67 @@
         <v>26</v>
       </c>
       <c r="D33" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E33" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F33">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="G33" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H33">
-        <v>30.007285</v>
+        <v>29.98347</v>
       </c>
       <c r="I33">
-        <v>74.126166</v>
+        <v>74.283652</v>
       </c>
       <c r="J33">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="K33">
-        <v>30.126927</v>
+        <v>30.090357</v>
       </c>
       <c r="L33">
-        <v>74.161942</v>
+        <v>74.20853700000001</v>
       </c>
       <c r="M33" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="N33">
-        <v>407</v>
+        <v>394</v>
       </c>
       <c r="O33" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P33" t="s">
         <v>26</v>
       </c>
       <c r="Q33" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R33" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S33">
-        <v>30.126927</v>
+        <v>30.08793156</v>
       </c>
       <c r="T33">
-        <v>74.161942</v>
+        <v>74.20908439</v>
       </c>
       <c r="U33" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="V33">
-        <v>28245</v>
+        <v>34094</v>
       </c>
       <c r="W33" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="X33" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
     </row>
     <row r="34" spans="1:24">
@@ -3319,67 +3280,67 @@
         <v>26</v>
       </c>
       <c r="D34" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E34" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F34">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="G34" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H34">
-        <v>30.039412</v>
+        <v>30.216512</v>
       </c>
       <c r="I34">
-        <v>73.954567</v>
+        <v>74.269492</v>
       </c>
       <c r="J34">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="K34">
-        <v>30.126927</v>
+        <v>30.163017</v>
       </c>
       <c r="L34">
-        <v>74.161942</v>
+        <v>74.186234</v>
       </c>
       <c r="M34" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="N34">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="O34" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P34" t="s">
         <v>26</v>
       </c>
       <c r="Q34" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R34" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S34">
-        <v>30.126927</v>
+        <v>30.1689126</v>
       </c>
       <c r="T34">
-        <v>74.161942</v>
+        <v>74.183232</v>
       </c>
       <c r="U34" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="V34">
-        <v>12854</v>
+        <v>10795.5</v>
       </c>
       <c r="W34" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="X34" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
     </row>
     <row r="35" spans="1:24">
@@ -3393,67 +3354,67 @@
         <v>26</v>
       </c>
       <c r="D35" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E35" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F35">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="G35" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H35">
-        <v>30.012837</v>
+        <v>30.216512</v>
       </c>
       <c r="I35">
-        <v>74.432883</v>
+        <v>74.269492</v>
       </c>
       <c r="J35">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="K35">
-        <v>30.090357</v>
+        <v>30.175344</v>
       </c>
       <c r="L35">
-        <v>74.20853700000001</v>
+        <v>74.178363</v>
       </c>
       <c r="M35" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="N35">
-        <v>397</v>
+        <v>406</v>
       </c>
       <c r="O35" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P35" t="s">
         <v>26</v>
       </c>
       <c r="Q35" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R35" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S35">
-        <v>30.0974593</v>
+        <v>30.16991135</v>
       </c>
       <c r="T35">
-        <v>74.206666</v>
+        <v>74.18230296</v>
       </c>
       <c r="U35" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="V35">
-        <v>74081</v>
+        <v>21605.5</v>
       </c>
       <c r="W35" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="X35" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
     </row>
     <row r="36" spans="1:24">
@@ -3467,67 +3428,67 @@
         <v>26</v>
       </c>
       <c r="D36" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E36" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F36">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="G36" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="H36">
-        <v>30.127701</v>
+        <v>30.132598</v>
       </c>
       <c r="I36">
-        <v>74.06368999999999</v>
+        <v>74.343463</v>
       </c>
       <c r="J36">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="K36">
-        <v>30.126927</v>
+        <v>30.100105</v>
       </c>
       <c r="L36">
-        <v>74.161942</v>
+        <v>74.20670699999999</v>
       </c>
       <c r="M36" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="N36">
-        <v>407</v>
+        <v>397</v>
       </c>
       <c r="O36" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P36" t="s">
         <v>26</v>
       </c>
       <c r="Q36" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R36" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S36">
-        <v>30.126927</v>
+        <v>30.0974593</v>
       </c>
       <c r="T36">
-        <v>74.161942</v>
+        <v>74.206666</v>
       </c>
       <c r="U36" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="V36">
-        <v>21311</v>
+        <v>71196</v>
       </c>
       <c r="W36" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="X36" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
     </row>
     <row r="37" spans="1:24">
@@ -3541,67 +3502,67 @@
         <v>26</v>
       </c>
       <c r="D37" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E37" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F37">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="G37" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="H37">
-        <v>29.98347</v>
+        <v>30.132598</v>
       </c>
       <c r="I37">
-        <v>74.283652</v>
+        <v>74.343463</v>
       </c>
       <c r="J37">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="K37">
-        <v>30.090357</v>
+        <v>30.126927</v>
       </c>
       <c r="L37">
-        <v>74.20853700000001</v>
+        <v>74.161942</v>
       </c>
       <c r="M37" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="N37">
-        <v>394</v>
+        <v>407</v>
       </c>
       <c r="O37" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P37" t="s">
         <v>26</v>
       </c>
       <c r="Q37" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R37" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S37">
-        <v>30.08793156</v>
+        <v>30.126927</v>
       </c>
       <c r="T37">
-        <v>74.20908439</v>
+        <v>74.161942</v>
       </c>
       <c r="U37" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="V37">
-        <v>30310</v>
+        <v>2489</v>
       </c>
       <c r="W37" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="X37" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
     </row>
     <row r="38" spans="1:24">
@@ -3615,67 +3576,67 @@
         <v>26</v>
       </c>
       <c r="D38" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E38" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F38">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="G38" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H38">
-        <v>29.98347</v>
+        <v>30.065633</v>
       </c>
       <c r="I38">
-        <v>74.283652</v>
+        <v>73.98462499999999</v>
       </c>
       <c r="J38">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="K38">
-        <v>30.090357</v>
+        <v>30.126927</v>
       </c>
       <c r="L38">
-        <v>74.20853700000001</v>
+        <v>74.161942</v>
       </c>
       <c r="M38" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="N38">
-        <v>395</v>
+        <v>407</v>
       </c>
       <c r="O38" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P38" t="s">
         <v>26</v>
       </c>
       <c r="Q38" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R38" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S38">
-        <v>30.08675444</v>
+        <v>30.126927</v>
       </c>
       <c r="T38">
-        <v>74.20888524</v>
+        <v>74.161942</v>
       </c>
       <c r="U38" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="V38">
-        <v>3784</v>
+        <v>34208</v>
       </c>
       <c r="W38" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="X38" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
     </row>
     <row r="39" spans="1:24">
@@ -3689,67 +3650,67 @@
         <v>26</v>
       </c>
       <c r="D39" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E39" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F39">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="G39" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H39">
-        <v>30.216512</v>
+        <v>30.224829</v>
       </c>
       <c r="I39">
-        <v>74.269492</v>
+        <v>74.12361199999999</v>
       </c>
       <c r="J39">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="K39">
-        <v>30.175344</v>
+        <v>30.180346</v>
       </c>
       <c r="L39">
-        <v>74.178363</v>
+        <v>74.17439299999999</v>
       </c>
       <c r="M39" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="N39">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="O39" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P39" t="s">
         <v>26</v>
       </c>
       <c r="Q39" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R39" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S39">
-        <v>30.17081207</v>
+        <v>30.15809938</v>
       </c>
       <c r="T39">
-        <v>74.18179719</v>
+        <v>74.16401603</v>
       </c>
       <c r="U39" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="V39">
-        <v>32401</v>
+        <v>54819.5</v>
       </c>
       <c r="W39" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="X39" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
     </row>
     <row r="40" spans="1:24">
@@ -3763,22 +3724,22 @@
         <v>26</v>
       </c>
       <c r="D40" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E40" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F40">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="G40" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="H40">
-        <v>30.132598</v>
+        <v>30.178444</v>
       </c>
       <c r="I40">
-        <v>74.343463</v>
+        <v>74.065141</v>
       </c>
       <c r="J40">
         <v>287</v>
@@ -3790,22 +3751,22 @@
         <v>74.161942</v>
       </c>
       <c r="M40" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="N40">
         <v>407</v>
       </c>
       <c r="O40" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P40" t="s">
         <v>26</v>
       </c>
       <c r="Q40" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R40" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S40">
         <v>30.126927</v>
@@ -3814,16 +3775,16 @@
         <v>74.161942</v>
       </c>
       <c r="U40" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="V40">
-        <v>73685</v>
+        <v>37768</v>
       </c>
       <c r="W40" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="X40" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
     </row>
     <row r="41" spans="1:24">
@@ -3837,22 +3798,22 @@
         <v>26</v>
       </c>
       <c r="D41" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E41" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F41">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="G41" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H41">
-        <v>30.065633</v>
+        <v>30.196706</v>
       </c>
       <c r="I41">
-        <v>73.98462499999999</v>
+        <v>74.04839699999999</v>
       </c>
       <c r="J41">
         <v>287</v>
@@ -3864,22 +3825,22 @@
         <v>74.161942</v>
       </c>
       <c r="M41" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="N41">
         <v>407</v>
       </c>
       <c r="O41" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P41" t="s">
         <v>26</v>
       </c>
       <c r="Q41" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R41" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S41">
         <v>30.126927</v>
@@ -3888,16 +3849,16 @@
         <v>74.161942</v>
       </c>
       <c r="U41" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="V41">
-        <v>34208</v>
+        <v>29874.5</v>
       </c>
       <c r="W41" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="X41" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
     </row>
     <row r="42" spans="1:24">
@@ -3911,67 +3872,67 @@
         <v>26</v>
       </c>
       <c r="D42" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E42" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F42">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="G42" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="H42">
-        <v>29.956267</v>
+        <v>30.035803</v>
       </c>
       <c r="I42">
-        <v>74.332578</v>
+        <v>74.111367</v>
       </c>
       <c r="J42">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="K42">
-        <v>30.090357</v>
+        <v>30.126927</v>
       </c>
       <c r="L42">
-        <v>74.20853700000001</v>
+        <v>74.161942</v>
       </c>
       <c r="M42" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="N42">
-        <v>394</v>
+        <v>407</v>
       </c>
       <c r="O42" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P42" t="s">
         <v>26</v>
       </c>
       <c r="Q42" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R42" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S42">
-        <v>30.08793156</v>
+        <v>30.126927</v>
       </c>
       <c r="T42">
-        <v>74.20908439</v>
+        <v>74.161942</v>
       </c>
       <c r="U42" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="V42">
-        <v>17701</v>
+        <v>56983.5</v>
       </c>
       <c r="W42" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="X42" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
     </row>
     <row r="43" spans="1:24">
@@ -3985,67 +3946,67 @@
         <v>26</v>
       </c>
       <c r="D43" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E43" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F43">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="G43" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="H43">
-        <v>30.224829</v>
+        <v>30.131281</v>
       </c>
       <c r="I43">
-        <v>74.12361199999999</v>
+        <v>74.103374</v>
       </c>
       <c r="J43">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="K43">
-        <v>30.180346</v>
+        <v>30.126927</v>
       </c>
       <c r="L43">
-        <v>74.17439299999999</v>
+        <v>74.161942</v>
       </c>
       <c r="M43" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="N43">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="O43" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P43" t="s">
         <v>26</v>
       </c>
       <c r="Q43" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R43" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S43">
-        <v>30.15809938</v>
+        <v>30.126927</v>
       </c>
       <c r="T43">
-        <v>74.16401603</v>
+        <v>74.161942</v>
       </c>
       <c r="U43" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="V43">
-        <v>54819.5</v>
+        <v>23195.5</v>
       </c>
       <c r="W43" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="X43" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
     </row>
     <row r="44" spans="1:24">
@@ -4059,22 +4020,22 @@
         <v>26</v>
       </c>
       <c r="D44" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E44" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F44">
-        <v>532</v>
+        <v>538</v>
       </c>
       <c r="G44" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H44">
-        <v>30.178444</v>
+        <v>30.029455</v>
       </c>
       <c r="I44">
-        <v>74.065141</v>
+        <v>74.077962</v>
       </c>
       <c r="J44">
         <v>287</v>
@@ -4086,22 +4047,22 @@
         <v>74.161942</v>
       </c>
       <c r="M44" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="N44">
         <v>407</v>
       </c>
       <c r="O44" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P44" t="s">
         <v>26</v>
       </c>
       <c r="Q44" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R44" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S44">
         <v>30.126927</v>
@@ -4110,16 +4071,16 @@
         <v>74.161942</v>
       </c>
       <c r="U44" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="V44">
-        <v>37768</v>
+        <v>57368</v>
       </c>
       <c r="W44" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="X44" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
     </row>
     <row r="45" spans="1:24">
@@ -4133,67 +4094,67 @@
         <v>26</v>
       </c>
       <c r="D45" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E45" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F45">
-        <v>533</v>
+        <v>540</v>
       </c>
       <c r="G45" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="H45">
-        <v>30.196706</v>
+        <v>29.983545</v>
       </c>
       <c r="I45">
-        <v>74.04839699999999</v>
+        <v>74.173574</v>
       </c>
       <c r="J45">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="K45">
-        <v>30.126927</v>
+        <v>30.105887</v>
       </c>
       <c r="L45">
-        <v>74.161942</v>
+        <v>74.18092900000001</v>
       </c>
       <c r="M45" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="N45">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="O45" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P45" t="s">
         <v>26</v>
       </c>
       <c r="Q45" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R45" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S45">
-        <v>30.126927</v>
+        <v>30.10552983</v>
       </c>
       <c r="T45">
-        <v>74.161942</v>
+        <v>74.18014506</v>
       </c>
       <c r="U45" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="V45">
-        <v>29874.5</v>
+        <v>2487</v>
       </c>
       <c r="W45" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="X45" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
     </row>
     <row r="46" spans="1:24">
@@ -4207,67 +4168,67 @@
         <v>26</v>
       </c>
       <c r="D46" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E46" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F46">
-        <v>534</v>
+        <v>541</v>
       </c>
       <c r="G46" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="H46">
-        <v>30.035803</v>
+        <v>30.254422</v>
       </c>
       <c r="I46">
-        <v>74.111367</v>
+        <v>74.126414</v>
       </c>
       <c r="J46">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="K46">
-        <v>30.126927</v>
+        <v>30.180346</v>
       </c>
       <c r="L46">
-        <v>74.161942</v>
+        <v>74.17439299999999</v>
       </c>
       <c r="M46" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="N46">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="O46" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P46" t="s">
         <v>26</v>
       </c>
       <c r="Q46" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R46" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S46">
-        <v>30.126927</v>
+        <v>30.15809938</v>
       </c>
       <c r="T46">
-        <v>74.161942</v>
+        <v>74.16401603</v>
       </c>
       <c r="U46" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="V46">
-        <v>56983.5</v>
+        <v>29195</v>
       </c>
       <c r="W46" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="X46" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
     </row>
     <row r="47" spans="1:24">
@@ -4281,67 +4242,67 @@
         <v>26</v>
       </c>
       <c r="D47" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E47" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F47">
-        <v>535</v>
+        <v>542</v>
       </c>
       <c r="G47" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H47">
-        <v>30.131281</v>
+        <v>30.247905</v>
       </c>
       <c r="I47">
-        <v>74.103374</v>
+        <v>74.129536</v>
       </c>
       <c r="J47">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="K47">
-        <v>30.126927</v>
+        <v>30.180346</v>
       </c>
       <c r="L47">
-        <v>74.161942</v>
+        <v>74.17439299999999</v>
       </c>
       <c r="M47" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="N47">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="O47" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P47" t="s">
         <v>26</v>
       </c>
       <c r="Q47" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R47" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S47">
-        <v>30.126927</v>
+        <v>30.15809938</v>
       </c>
       <c r="T47">
-        <v>74.161942</v>
+        <v>74.16401603</v>
       </c>
       <c r="U47" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="V47">
-        <v>23195.5</v>
+        <v>26795</v>
       </c>
       <c r="W47" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="X47" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
     </row>
     <row r="48" spans="1:24">
@@ -4355,67 +4316,67 @@
         <v>26</v>
       </c>
       <c r="D48" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E48" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F48">
-        <v>536</v>
+        <v>543</v>
       </c>
       <c r="G48" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="H48">
-        <v>30.027734</v>
+        <v>30.25374</v>
       </c>
       <c r="I48">
-        <v>74.36728100000001</v>
+        <v>74.122122</v>
       </c>
       <c r="J48">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="K48">
-        <v>30.090357</v>
+        <v>30.180346</v>
       </c>
       <c r="L48">
-        <v>74.20853700000001</v>
+        <v>74.17439299999999</v>
       </c>
       <c r="M48" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="N48">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="O48" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P48" t="s">
         <v>26</v>
       </c>
       <c r="Q48" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R48" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S48">
-        <v>30.08793156</v>
+        <v>30.15809938</v>
       </c>
       <c r="T48">
-        <v>74.20908439</v>
+        <v>74.16401603</v>
       </c>
       <c r="U48" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="V48">
-        <v>71340</v>
+        <v>7950</v>
       </c>
       <c r="W48" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="X48" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
     </row>
     <row r="49" spans="1:24">
@@ -4429,67 +4390,67 @@
         <v>26</v>
       </c>
       <c r="D49" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E49" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F49">
-        <v>536</v>
+        <v>545</v>
       </c>
       <c r="G49" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H49">
-        <v>30.027734</v>
+        <v>29.975306</v>
       </c>
       <c r="I49">
-        <v>74.36728100000001</v>
+        <v>74.164011</v>
       </c>
       <c r="J49">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="K49">
-        <v>30.090357</v>
+        <v>30.105887</v>
       </c>
       <c r="L49">
-        <v>74.20853700000001</v>
+        <v>74.18092900000001</v>
       </c>
       <c r="M49" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="N49">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="O49" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P49" t="s">
         <v>26</v>
       </c>
       <c r="Q49" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R49" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S49">
-        <v>30.0974593</v>
+        <v>30.10552983</v>
       </c>
       <c r="T49">
-        <v>74.206666</v>
+        <v>74.18014506</v>
       </c>
       <c r="U49" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="V49">
-        <v>36210</v>
+        <v>5500</v>
       </c>
       <c r="W49" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="X49" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
     </row>
     <row r="50" spans="1:24">
@@ -4503,67 +4464,67 @@
         <v>26</v>
       </c>
       <c r="D50" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E50" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F50">
-        <v>537</v>
+        <v>546</v>
       </c>
       <c r="G50" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H50">
-        <v>29.951208</v>
+        <v>30.144184</v>
       </c>
       <c r="I50">
-        <v>74.380385</v>
+        <v>74.122771</v>
       </c>
       <c r="J50">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="K50">
-        <v>30.090357</v>
+        <v>30.126927</v>
       </c>
       <c r="L50">
-        <v>74.20853700000001</v>
+        <v>74.161942</v>
       </c>
       <c r="M50" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="N50">
-        <v>394</v>
+        <v>407</v>
       </c>
       <c r="O50" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P50" t="s">
         <v>26</v>
       </c>
       <c r="Q50" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R50" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S50">
-        <v>30.08793156</v>
+        <v>30.126927</v>
       </c>
       <c r="T50">
-        <v>74.20908439</v>
+        <v>74.161942</v>
       </c>
       <c r="U50" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="V50">
-        <v>43549</v>
+        <v>12630.5</v>
       </c>
       <c r="W50" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="X50" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
     </row>
     <row r="51" spans="1:24">
@@ -4577,22 +4538,22 @@
         <v>26</v>
       </c>
       <c r="D51" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E51" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F51">
-        <v>538</v>
+        <v>547</v>
       </c>
       <c r="G51" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H51">
-        <v>30.029455</v>
+        <v>30.161715</v>
       </c>
       <c r="I51">
-        <v>74.077962</v>
+        <v>73.987483</v>
       </c>
       <c r="J51">
         <v>287</v>
@@ -4604,22 +4565,22 @@
         <v>74.161942</v>
       </c>
       <c r="M51" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="N51">
         <v>407</v>
       </c>
       <c r="O51" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P51" t="s">
         <v>26</v>
       </c>
       <c r="Q51" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R51" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S51">
         <v>30.126927</v>
@@ -4628,16 +4589,16 @@
         <v>74.161942</v>
       </c>
       <c r="U51" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="V51">
-        <v>57368</v>
+        <v>13803</v>
       </c>
       <c r="W51" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="X51" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
     </row>
     <row r="52" spans="1:24">
@@ -4651,22 +4612,22 @@
         <v>26</v>
       </c>
       <c r="D52" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E52" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F52">
-        <v>540</v>
+        <v>548</v>
       </c>
       <c r="G52" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H52">
-        <v>29.983545</v>
+        <v>30.21135</v>
       </c>
       <c r="I52">
-        <v>74.173574</v>
+        <v>74.02397999999999</v>
       </c>
       <c r="J52">
         <v>287</v>
@@ -4678,22 +4639,22 @@
         <v>74.161942</v>
       </c>
       <c r="M52" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="N52">
         <v>407</v>
       </c>
       <c r="O52" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P52" t="s">
         <v>26</v>
       </c>
       <c r="Q52" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R52" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S52">
         <v>30.126927</v>
@@ -4702,16 +4663,16 @@
         <v>74.161942</v>
       </c>
       <c r="U52" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="V52">
-        <v>2487</v>
+        <v>9145</v>
       </c>
       <c r="W52" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="X52" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
     </row>
     <row r="53" spans="1:24">
@@ -4725,67 +4686,67 @@
         <v>26</v>
       </c>
       <c r="D53" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E53" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F53">
-        <v>541</v>
+        <v>549</v>
       </c>
       <c r="G53" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H53">
-        <v>30.254422</v>
+        <v>30.296726</v>
       </c>
       <c r="I53">
-        <v>74.126414</v>
+        <v>74.263169</v>
       </c>
       <c r="J53">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="K53">
-        <v>30.180346</v>
+        <v>30.175344</v>
       </c>
       <c r="L53">
-        <v>74.17439299999999</v>
+        <v>74.178363</v>
       </c>
       <c r="M53" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="N53">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="O53" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P53" t="s">
         <v>26</v>
       </c>
       <c r="Q53" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R53" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S53">
-        <v>30.15809938</v>
+        <v>30.17081207</v>
       </c>
       <c r="T53">
-        <v>74.16401603</v>
+        <v>74.18179719</v>
       </c>
       <c r="U53" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="V53">
-        <v>29195</v>
+        <v>17622.5</v>
       </c>
       <c r="W53" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="X53" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
     </row>
     <row r="54" spans="1:24">
@@ -4799,22 +4760,22 @@
         <v>26</v>
       </c>
       <c r="D54" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E54" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F54">
-        <v>542</v>
+        <v>550</v>
       </c>
       <c r="G54" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H54">
-        <v>30.247905</v>
+        <v>30.285139</v>
       </c>
       <c r="I54">
-        <v>74.129536</v>
+        <v>74.172681</v>
       </c>
       <c r="J54">
         <v>285</v>
@@ -4826,22 +4787,22 @@
         <v>74.17439299999999</v>
       </c>
       <c r="M54" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="N54">
         <v>400</v>
       </c>
       <c r="O54" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P54" t="s">
         <v>26</v>
       </c>
       <c r="Q54" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R54" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S54">
         <v>30.15809938</v>
@@ -4850,16 +4811,16 @@
         <v>74.16401603</v>
       </c>
       <c r="U54" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="V54">
-        <v>26795</v>
+        <v>2347.5</v>
       </c>
       <c r="W54" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="X54" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
     </row>
     <row r="55" spans="1:24">
@@ -4873,22 +4834,22 @@
         <v>26</v>
       </c>
       <c r="D55" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E55" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F55">
-        <v>543</v>
+        <v>550</v>
       </c>
       <c r="G55" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="H55">
-        <v>30.25374</v>
+        <v>30.285139</v>
       </c>
       <c r="I55">
-        <v>74.122122</v>
+        <v>74.172681</v>
       </c>
       <c r="J55">
         <v>285</v>
@@ -4900,40 +4861,40 @@
         <v>74.17439299999999</v>
       </c>
       <c r="M55" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="N55">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="O55" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P55" t="s">
         <v>26</v>
       </c>
       <c r="Q55" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R55" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S55">
-        <v>30.15809938</v>
+        <v>30.17767461</v>
       </c>
       <c r="T55">
-        <v>74.16401603</v>
+        <v>74.17723581</v>
       </c>
       <c r="U55" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="V55">
-        <v>7950</v>
+        <v>40337.5</v>
       </c>
       <c r="W55" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="X55" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
     </row>
     <row r="56" spans="1:24">
@@ -4947,67 +4908,67 @@
         <v>26</v>
       </c>
       <c r="D56" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E56" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F56">
-        <v>545</v>
+        <v>551</v>
       </c>
       <c r="G56" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H56">
-        <v>29.975306</v>
+        <v>30.260814</v>
       </c>
       <c r="I56">
-        <v>74.164011</v>
+        <v>74.269329</v>
       </c>
       <c r="J56">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="K56">
-        <v>30.126927</v>
+        <v>30.175344</v>
       </c>
       <c r="L56">
-        <v>74.161942</v>
+        <v>74.178363</v>
       </c>
       <c r="M56" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="N56">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="O56" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P56" t="s">
         <v>26</v>
       </c>
       <c r="Q56" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R56" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S56">
-        <v>30.126927</v>
+        <v>30.17081207</v>
       </c>
       <c r="T56">
-        <v>74.161942</v>
+        <v>74.18179719</v>
       </c>
       <c r="U56" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="V56">
-        <v>5500</v>
+        <v>56502.5</v>
       </c>
       <c r="W56" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="X56" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
     </row>
     <row r="57" spans="1:24">
@@ -5021,67 +4982,67 @@
         <v>26</v>
       </c>
       <c r="D57" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E57" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F57">
-        <v>546</v>
+        <v>552</v>
       </c>
       <c r="G57" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="H57">
-        <v>30.144184</v>
+        <v>30.290503</v>
       </c>
       <c r="I57">
-        <v>74.122771</v>
+        <v>74.220803</v>
       </c>
       <c r="J57">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="K57">
-        <v>30.126927</v>
+        <v>30.175344</v>
       </c>
       <c r="L57">
-        <v>74.161942</v>
+        <v>74.178363</v>
       </c>
       <c r="M57" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="N57">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="O57" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P57" t="s">
         <v>26</v>
       </c>
       <c r="Q57" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R57" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S57">
-        <v>30.126927</v>
+        <v>30.17081207</v>
       </c>
       <c r="T57">
-        <v>74.161942</v>
+        <v>74.18179719</v>
       </c>
       <c r="U57" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="V57">
-        <v>12630.5</v>
+        <v>43110</v>
       </c>
       <c r="W57" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="X57" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
     </row>
     <row r="58" spans="1:24">
@@ -5095,67 +5056,67 @@
         <v>26</v>
       </c>
       <c r="D58" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E58" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F58">
-        <v>547</v>
+        <v>560</v>
       </c>
       <c r="G58" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H58">
-        <v>30.161715</v>
+        <v>30.251211</v>
       </c>
       <c r="I58">
-        <v>73.987483</v>
+        <v>74.011872</v>
       </c>
       <c r="J58">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="K58">
-        <v>30.126927</v>
+        <v>30.180346</v>
       </c>
       <c r="L58">
-        <v>74.161942</v>
+        <v>74.17439299999999</v>
       </c>
       <c r="M58" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="N58">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="O58" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P58" t="s">
         <v>26</v>
       </c>
       <c r="Q58" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R58" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S58">
-        <v>30.126927</v>
+        <v>30.15809938</v>
       </c>
       <c r="T58">
-        <v>74.161942</v>
+        <v>74.16401603</v>
       </c>
       <c r="U58" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="V58">
-        <v>13803</v>
+        <v>128218</v>
       </c>
       <c r="W58" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="X58" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
     </row>
     <row r="59" spans="1:24">
@@ -5169,22 +5130,22 @@
         <v>26</v>
       </c>
       <c r="D59" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E59" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F59">
-        <v>548</v>
+        <v>565</v>
       </c>
       <c r="G59" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="H59">
-        <v>30.21135</v>
+        <v>30.280985</v>
       </c>
       <c r="I59">
-        <v>74.02397999999999</v>
+        <v>74.057811</v>
       </c>
       <c r="J59">
         <v>285</v>
@@ -5196,22 +5157,22 @@
         <v>74.17439299999999</v>
       </c>
       <c r="M59" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="N59">
         <v>400</v>
       </c>
       <c r="O59" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P59" t="s">
         <v>26</v>
       </c>
       <c r="Q59" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R59" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S59">
         <v>30.15809938</v>
@@ -5220,16 +5181,16 @@
         <v>74.16401603</v>
       </c>
       <c r="U59" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="V59">
-        <v>9145</v>
+        <v>62709.5</v>
       </c>
       <c r="W59" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="X59" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
     </row>
     <row r="60" spans="1:24">
@@ -5243,22 +5204,22 @@
         <v>26</v>
       </c>
       <c r="D60" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E60" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F60">
-        <v>549</v>
+        <v>612</v>
       </c>
       <c r="G60" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H60">
-        <v>30.296726</v>
+        <v>30.3064</v>
       </c>
       <c r="I60">
-        <v>74.263169</v>
+        <v>74.22073899999999</v>
       </c>
       <c r="J60">
         <v>279</v>
@@ -5270,22 +5231,22 @@
         <v>74.178363</v>
       </c>
       <c r="M60" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="N60">
         <v>401</v>
       </c>
       <c r="O60" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P60" t="s">
         <v>26</v>
       </c>
       <c r="Q60" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R60" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S60">
         <v>30.17081207</v>
@@ -5294,16 +5255,16 @@
         <v>74.18179719</v>
       </c>
       <c r="U60" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="V60">
-        <v>17622.5</v>
+        <v>47189.5</v>
       </c>
       <c r="W60" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="X60" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
     </row>
     <row r="61" spans="1:24">
@@ -5320,37 +5281,37 @@
         <v>29</v>
       </c>
       <c r="E61" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F61">
-        <v>550</v>
+        <v>1046</v>
       </c>
       <c r="G61" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="H61">
-        <v>30.285139</v>
+        <v>31.425406</v>
       </c>
       <c r="I61">
-        <v>74.172681</v>
+        <v>75.719528</v>
       </c>
       <c r="J61">
-        <v>285</v>
+        <v>522</v>
       </c>
       <c r="K61">
-        <v>30.180346</v>
+        <v>31.4204409</v>
       </c>
       <c r="L61">
-        <v>74.17439299999999</v>
+        <v>75.69994199999999</v>
       </c>
       <c r="M61" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="N61">
-        <v>402</v>
+        <v>625</v>
       </c>
       <c r="O61" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P61" t="s">
         <v>26</v>
@@ -5359,25 +5320,25 @@
         <v>29</v>
       </c>
       <c r="R61" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S61">
-        <v>30.17767461</v>
+        <v>31.408658</v>
       </c>
       <c r="T61">
-        <v>74.17723581</v>
+        <v>75.685958</v>
       </c>
       <c r="U61" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="V61">
-        <v>42685</v>
+        <v>21500</v>
       </c>
       <c r="W61" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="X61" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
     </row>
     <row r="62" spans="1:24">
@@ -5391,67 +5352,67 @@
         <v>26</v>
       </c>
       <c r="D62" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E62" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F62">
-        <v>551</v>
+        <v>1577</v>
       </c>
       <c r="G62" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="H62">
-        <v>30.260814</v>
+        <v>30.4426709</v>
       </c>
       <c r="I62">
-        <v>74.269329</v>
+        <v>74.4101264</v>
       </c>
       <c r="J62">
-        <v>279</v>
+        <v>1455</v>
       </c>
       <c r="K62">
-        <v>30.175344</v>
+        <v>30.450458</v>
       </c>
       <c r="L62">
-        <v>74.178363</v>
+        <v>74.489422</v>
       </c>
       <c r="M62" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="N62">
-        <v>401</v>
+        <v>866</v>
       </c>
       <c r="O62" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P62" t="s">
         <v>26</v>
       </c>
       <c r="Q62" t="s">
-        <v>29</v>
+        <v>88</v>
       </c>
       <c r="R62" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S62">
-        <v>30.17081207</v>
+        <v>30.458388</v>
       </c>
       <c r="T62">
-        <v>74.18179719</v>
+        <v>74.453514</v>
       </c>
       <c r="U62" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="V62">
-        <v>56502.5</v>
+        <v>88594</v>
       </c>
       <c r="W62" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="X62" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
     </row>
     <row r="63" spans="1:24">
@@ -5465,67 +5426,67 @@
         <v>26</v>
       </c>
       <c r="D63" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E63" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F63">
-        <v>552</v>
+        <v>1577</v>
       </c>
       <c r="G63" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="H63">
-        <v>30.290503</v>
+        <v>30.4426709</v>
       </c>
       <c r="I63">
-        <v>74.220803</v>
+        <v>74.4101264</v>
       </c>
       <c r="J63">
-        <v>279</v>
+        <v>1455</v>
       </c>
       <c r="K63">
-        <v>30.175344</v>
+        <v>30.450458</v>
       </c>
       <c r="L63">
-        <v>74.178363</v>
+        <v>74.489422</v>
       </c>
       <c r="M63" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="N63">
-        <v>401</v>
+        <v>870</v>
       </c>
       <c r="O63" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P63" t="s">
         <v>26</v>
       </c>
       <c r="Q63" t="s">
-        <v>29</v>
+        <v>88</v>
       </c>
       <c r="R63" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S63">
-        <v>30.17081207</v>
+        <v>30.458388</v>
       </c>
       <c r="T63">
-        <v>74.18179719</v>
+        <v>74.453514</v>
       </c>
       <c r="U63" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="V63">
-        <v>43110</v>
+        <v>10000</v>
       </c>
       <c r="W63" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="X63" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
     </row>
     <row r="64" spans="1:24">
@@ -5542,46 +5503,46 @@
         <v>30</v>
       </c>
       <c r="E64" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F64">
-        <v>1322</v>
+        <v>1577</v>
       </c>
       <c r="G64" t="s">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="H64">
-        <v>30.67924</v>
+        <v>30.4426709</v>
       </c>
       <c r="I64">
-        <v>75.84139999999999</v>
+        <v>74.4101264</v>
       </c>
       <c r="J64">
-        <v>703</v>
+        <v>1455</v>
       </c>
       <c r="K64">
-        <v>30.618135</v>
+        <v>30.450458</v>
       </c>
       <c r="L64">
-        <v>75.435686</v>
+        <v>74.489422</v>
       </c>
       <c r="M64" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="N64">
-        <v>864</v>
+        <v>875</v>
       </c>
       <c r="O64" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P64" t="s">
         <v>26</v>
       </c>
       <c r="Q64" t="s">
-        <v>30</v>
+        <v>88</v>
       </c>
       <c r="R64" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="S64">
         <v>30.458388</v>
@@ -5590,16 +5551,16 @@
         <v>74.453514</v>
       </c>
       <c r="U64" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="V64">
-        <v>197630</v>
+        <v>5000</v>
       </c>
       <c r="W64" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="X64" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
     </row>
     <row r="65" spans="1:24">
@@ -5616,46 +5577,46 @@
         <v>30</v>
       </c>
       <c r="E65" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F65">
-        <v>1322</v>
+        <v>1577</v>
       </c>
       <c r="G65" t="s">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="H65">
-        <v>30.67924</v>
+        <v>30.4426709</v>
       </c>
       <c r="I65">
-        <v>75.84139999999999</v>
+        <v>74.4101264</v>
       </c>
       <c r="J65">
-        <v>703</v>
+        <v>1455</v>
       </c>
       <c r="K65">
-        <v>30.618135</v>
+        <v>30.450458</v>
       </c>
       <c r="L65">
-        <v>75.435686</v>
+        <v>74.489422</v>
       </c>
       <c r="M65" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="N65">
-        <v>865</v>
+        <v>876</v>
       </c>
       <c r="O65" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P65" t="s">
         <v>26</v>
       </c>
       <c r="Q65" t="s">
-        <v>30</v>
+        <v>88</v>
       </c>
       <c r="R65" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="S65">
         <v>30.458388</v>
@@ -5664,16 +5625,16 @@
         <v>74.453514</v>
       </c>
       <c r="U65" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="V65">
-        <v>16680</v>
+        <v>5000</v>
       </c>
       <c r="W65" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="X65" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
     </row>
     <row r="66" spans="1:24">
@@ -5690,46 +5651,46 @@
         <v>30</v>
       </c>
       <c r="E66" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F66">
-        <v>1322</v>
+        <v>1597</v>
       </c>
       <c r="G66" t="s">
-        <v>34</v>
+        <v>82</v>
       </c>
       <c r="H66">
-        <v>30.67924</v>
+        <v>30.419565</v>
       </c>
       <c r="I66">
-        <v>75.84139999999999</v>
+        <v>74.44302166999999</v>
       </c>
       <c r="J66">
-        <v>703</v>
+        <v>1455</v>
       </c>
       <c r="K66">
-        <v>30.618135</v>
+        <v>30.450458</v>
       </c>
       <c r="L66">
-        <v>75.435686</v>
+        <v>74.489422</v>
       </c>
       <c r="M66" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="N66">
         <v>866</v>
       </c>
       <c r="O66" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P66" t="s">
         <v>26</v>
       </c>
       <c r="Q66" t="s">
-        <v>30</v>
+        <v>88</v>
       </c>
       <c r="R66" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="S66">
         <v>30.458388</v>
@@ -5738,16 +5699,16 @@
         <v>74.453514</v>
       </c>
       <c r="U66" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="V66">
-        <v>42630</v>
+        <v>38086</v>
       </c>
       <c r="W66" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="X66" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
     </row>
     <row r="67" spans="1:24">
@@ -5764,46 +5725,46 @@
         <v>30</v>
       </c>
       <c r="E67" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F67">
-        <v>1322</v>
+        <v>1597</v>
       </c>
       <c r="G67" t="s">
-        <v>34</v>
+        <v>82</v>
       </c>
       <c r="H67">
-        <v>30.67924</v>
+        <v>30.419565</v>
       </c>
       <c r="I67">
-        <v>75.84139999999999</v>
+        <v>74.44302166999999</v>
       </c>
       <c r="J67">
-        <v>703</v>
+        <v>1455</v>
       </c>
       <c r="K67">
-        <v>30.618135</v>
+        <v>30.450458</v>
       </c>
       <c r="L67">
-        <v>75.435686</v>
+        <v>74.489422</v>
       </c>
       <c r="M67" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="N67">
-        <v>868</v>
+        <v>872</v>
       </c>
       <c r="O67" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P67" t="s">
         <v>26</v>
       </c>
       <c r="Q67" t="s">
-        <v>30</v>
+        <v>88</v>
       </c>
       <c r="R67" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="S67">
         <v>30.458388</v>
@@ -5812,16 +5773,16 @@
         <v>74.453514</v>
       </c>
       <c r="U67" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="V67">
-        <v>10000</v>
+        <v>30720</v>
       </c>
       <c r="W67" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="X67" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
     </row>
     <row r="68" spans="1:24">
@@ -5838,46 +5799,46 @@
         <v>30</v>
       </c>
       <c r="E68" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F68">
-        <v>1322</v>
+        <v>1597</v>
       </c>
       <c r="G68" t="s">
-        <v>34</v>
+        <v>82</v>
       </c>
       <c r="H68">
-        <v>30.67924</v>
+        <v>30.419565</v>
       </c>
       <c r="I68">
-        <v>75.84139999999999</v>
+        <v>74.44302166999999</v>
       </c>
       <c r="J68">
-        <v>703</v>
+        <v>1455</v>
       </c>
       <c r="K68">
-        <v>30.618135</v>
+        <v>30.450458</v>
       </c>
       <c r="L68">
-        <v>75.435686</v>
+        <v>74.489422</v>
       </c>
       <c r="M68" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="N68">
-        <v>869</v>
+        <v>877</v>
       </c>
       <c r="O68" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P68" t="s">
         <v>26</v>
       </c>
       <c r="Q68" t="s">
-        <v>30</v>
+        <v>88</v>
       </c>
       <c r="R68" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="S68">
         <v>30.458388</v>
@@ -5886,16 +5847,16 @@
         <v>74.453514</v>
       </c>
       <c r="U68" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="V68">
-        <v>10000</v>
+        <v>5127</v>
       </c>
       <c r="W68" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="X68" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
     </row>
     <row r="69" spans="1:24">
@@ -5912,46 +5873,46 @@
         <v>30</v>
       </c>
       <c r="E69" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F69">
-        <v>1322</v>
+        <v>1607</v>
       </c>
       <c r="G69" t="s">
-        <v>34</v>
+        <v>83</v>
       </c>
       <c r="H69">
-        <v>30.67924</v>
+        <v>30.4726737</v>
       </c>
       <c r="I69">
-        <v>75.84139999999999</v>
+        <v>74.5049465</v>
       </c>
       <c r="J69">
-        <v>703</v>
+        <v>1512</v>
       </c>
       <c r="K69">
-        <v>30.618135</v>
+        <v>30.4713293</v>
       </c>
       <c r="L69">
-        <v>75.435686</v>
+        <v>74.5033904</v>
       </c>
       <c r="M69" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="N69">
-        <v>870</v>
+        <v>864</v>
       </c>
       <c r="O69" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P69" t="s">
         <v>26</v>
       </c>
       <c r="Q69" t="s">
-        <v>30</v>
+        <v>88</v>
       </c>
       <c r="R69" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="S69">
         <v>30.458388</v>
@@ -5960,16 +5921,16 @@
         <v>74.453514</v>
       </c>
       <c r="U69" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="V69">
-        <v>10000</v>
+        <v>294680</v>
       </c>
       <c r="W69" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="X69" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
     </row>
     <row r="70" spans="1:24">
@@ -5986,46 +5947,46 @@
         <v>30</v>
       </c>
       <c r="E70" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F70">
-        <v>1322</v>
+        <v>1607</v>
       </c>
       <c r="G70" t="s">
-        <v>34</v>
+        <v>83</v>
       </c>
       <c r="H70">
-        <v>30.67924</v>
+        <v>30.4726737</v>
       </c>
       <c r="I70">
-        <v>75.84139999999999</v>
+        <v>74.5049465</v>
       </c>
       <c r="J70">
-        <v>703</v>
+        <v>1512</v>
       </c>
       <c r="K70">
-        <v>30.618135</v>
+        <v>30.4713293</v>
       </c>
       <c r="L70">
-        <v>75.435686</v>
+        <v>74.5033904</v>
       </c>
       <c r="M70" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="N70">
-        <v>871</v>
+        <v>865</v>
       </c>
       <c r="O70" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P70" t="s">
         <v>26</v>
       </c>
       <c r="Q70" t="s">
-        <v>30</v>
+        <v>88</v>
       </c>
       <c r="R70" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="S70">
         <v>30.458388</v>
@@ -6034,16 +5995,16 @@
         <v>74.453514</v>
       </c>
       <c r="U70" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="V70">
-        <v>30720</v>
+        <v>16680</v>
       </c>
       <c r="W70" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="X70" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
     </row>
     <row r="71" spans="1:24">
@@ -6060,46 +6021,46 @@
         <v>30</v>
       </c>
       <c r="E71" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F71">
-        <v>1322</v>
+        <v>1607</v>
       </c>
       <c r="G71" t="s">
-        <v>34</v>
+        <v>83</v>
       </c>
       <c r="H71">
-        <v>30.67924</v>
+        <v>30.4726737</v>
       </c>
       <c r="I71">
-        <v>75.84139999999999</v>
+        <v>74.5049465</v>
       </c>
       <c r="J71">
-        <v>703</v>
+        <v>1512</v>
       </c>
       <c r="K71">
-        <v>30.618135</v>
+        <v>30.4713293</v>
       </c>
       <c r="L71">
-        <v>75.435686</v>
+        <v>74.5033904</v>
       </c>
       <c r="M71" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="N71">
-        <v>872</v>
+        <v>867</v>
       </c>
       <c r="O71" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P71" t="s">
         <v>26</v>
       </c>
       <c r="Q71" t="s">
-        <v>30</v>
+        <v>88</v>
       </c>
       <c r="R71" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="S71">
         <v>30.458388</v>
@@ -6108,16 +6069,16 @@
         <v>74.453514</v>
       </c>
       <c r="U71" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="V71">
-        <v>1080</v>
+        <v>10000</v>
       </c>
       <c r="W71" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="X71" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
     </row>
     <row r="72" spans="1:24">
@@ -6134,46 +6095,46 @@
         <v>30</v>
       </c>
       <c r="E72" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F72">
-        <v>1322</v>
+        <v>1607</v>
       </c>
       <c r="G72" t="s">
-        <v>34</v>
+        <v>83</v>
       </c>
       <c r="H72">
-        <v>30.67924</v>
+        <v>30.4726737</v>
       </c>
       <c r="I72">
-        <v>75.84139999999999</v>
+        <v>74.5049465</v>
       </c>
       <c r="J72">
-        <v>703</v>
+        <v>1512</v>
       </c>
       <c r="K72">
-        <v>30.618135</v>
+        <v>30.4713293</v>
       </c>
       <c r="L72">
-        <v>75.435686</v>
+        <v>74.5033904</v>
       </c>
       <c r="M72" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="N72">
-        <v>873</v>
+        <v>868</v>
       </c>
       <c r="O72" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P72" t="s">
         <v>26</v>
       </c>
       <c r="Q72" t="s">
-        <v>30</v>
+        <v>88</v>
       </c>
       <c r="R72" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="S72">
         <v>30.458388</v>
@@ -6182,16 +6143,16 @@
         <v>74.453514</v>
       </c>
       <c r="U72" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="V72">
-        <v>29640</v>
+        <v>10000</v>
       </c>
       <c r="W72" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="X72" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
     </row>
     <row r="73" spans="1:24">
@@ -6208,46 +6169,46 @@
         <v>30</v>
       </c>
       <c r="E73" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F73">
-        <v>1322</v>
+        <v>1607</v>
       </c>
       <c r="G73" t="s">
-        <v>34</v>
+        <v>83</v>
       </c>
       <c r="H73">
-        <v>30.67924</v>
+        <v>30.4726737</v>
       </c>
       <c r="I73">
-        <v>75.84139999999999</v>
+        <v>74.5049465</v>
       </c>
       <c r="J73">
-        <v>703</v>
+        <v>1512</v>
       </c>
       <c r="K73">
-        <v>30.618135</v>
+        <v>30.4713293</v>
       </c>
       <c r="L73">
-        <v>75.435686</v>
+        <v>74.5033904</v>
       </c>
       <c r="M73" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="N73">
-        <v>877</v>
+        <v>869</v>
       </c>
       <c r="O73" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P73" t="s">
         <v>26</v>
       </c>
       <c r="Q73" t="s">
-        <v>30</v>
+        <v>88</v>
       </c>
       <c r="R73" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="S73">
         <v>30.458388</v>
@@ -6256,16 +6217,16 @@
         <v>74.453514</v>
       </c>
       <c r="U73" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="V73">
-        <v>9950</v>
+        <v>10000</v>
       </c>
       <c r="W73" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="X73" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
     </row>
     <row r="74" spans="1:24">
@@ -6282,46 +6243,46 @@
         <v>30</v>
       </c>
       <c r="E74" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F74">
-        <v>1323</v>
+        <v>1607</v>
       </c>
       <c r="G74" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H74">
-        <v>30.61296</v>
+        <v>30.4726737</v>
       </c>
       <c r="I74">
-        <v>75.84106</v>
+        <v>74.5049465</v>
       </c>
       <c r="J74">
-        <v>999</v>
+        <v>1512</v>
       </c>
       <c r="K74">
-        <v>30.561546</v>
+        <v>30.4713293</v>
       </c>
       <c r="L74">
-        <v>75.352118</v>
+        <v>74.5033904</v>
       </c>
       <c r="M74" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="N74">
-        <v>867</v>
+        <v>871</v>
       </c>
       <c r="O74" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P74" t="s">
         <v>26</v>
       </c>
       <c r="Q74" t="s">
-        <v>30</v>
+        <v>88</v>
       </c>
       <c r="R74" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="S74">
         <v>30.458388</v>
@@ -6330,16 +6291,16 @@
         <v>74.453514</v>
       </c>
       <c r="U74" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="V74">
-        <v>10000</v>
+        <v>30720</v>
       </c>
       <c r="W74" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="X74" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
     </row>
     <row r="75" spans="1:24">
@@ -6356,46 +6317,46 @@
         <v>30</v>
       </c>
       <c r="E75" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F75">
-        <v>1323</v>
+        <v>1607</v>
       </c>
       <c r="G75" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H75">
-        <v>30.61296</v>
+        <v>30.4726737</v>
       </c>
       <c r="I75">
-        <v>75.84106</v>
+        <v>74.5049465</v>
       </c>
       <c r="J75">
-        <v>999</v>
+        <v>1512</v>
       </c>
       <c r="K75">
-        <v>30.561546</v>
+        <v>30.4713293</v>
       </c>
       <c r="L75">
-        <v>75.352118</v>
+        <v>74.5033904</v>
       </c>
       <c r="M75" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="N75">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="O75" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P75" t="s">
         <v>26</v>
       </c>
       <c r="Q75" t="s">
-        <v>30</v>
+        <v>88</v>
       </c>
       <c r="R75" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="S75">
         <v>30.458388</v>
@@ -6404,16 +6365,16 @@
         <v>74.453514</v>
       </c>
       <c r="U75" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="V75">
-        <v>5000</v>
+        <v>29640</v>
       </c>
       <c r="W75" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="X75" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
     </row>
     <row r="76" spans="1:24">
@@ -6430,46 +6391,46 @@
         <v>30</v>
       </c>
       <c r="E76" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F76">
-        <v>1323</v>
+        <v>1607</v>
       </c>
       <c r="G76" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H76">
-        <v>30.61296</v>
+        <v>30.4726737</v>
       </c>
       <c r="I76">
-        <v>75.84106</v>
+        <v>74.5049465</v>
       </c>
       <c r="J76">
-        <v>999</v>
+        <v>1512</v>
       </c>
       <c r="K76">
-        <v>30.561546</v>
+        <v>30.4713293</v>
       </c>
       <c r="L76">
-        <v>75.352118</v>
+        <v>74.5033904</v>
       </c>
       <c r="M76" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="N76">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="O76" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P76" t="s">
         <v>26</v>
       </c>
       <c r="Q76" t="s">
-        <v>30</v>
+        <v>88</v>
       </c>
       <c r="R76" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="S76">
         <v>30.458388</v>
@@ -6478,16 +6439,16 @@
         <v>74.453514</v>
       </c>
       <c r="U76" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="V76">
-        <v>5000</v>
+        <v>28460</v>
       </c>
       <c r="W76" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="X76" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
     </row>
     <row r="77" spans="1:24">
@@ -6504,46 +6465,46 @@
         <v>30</v>
       </c>
       <c r="E77" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F77">
-        <v>1323</v>
+        <v>1607</v>
       </c>
       <c r="G77" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H77">
-        <v>30.61296</v>
+        <v>30.4726737</v>
       </c>
       <c r="I77">
-        <v>75.84106</v>
+        <v>74.5049465</v>
       </c>
       <c r="J77">
-        <v>999</v>
+        <v>1512</v>
       </c>
       <c r="K77">
-        <v>30.561546</v>
+        <v>30.4713293</v>
       </c>
       <c r="L77">
-        <v>75.352118</v>
+        <v>74.5033904</v>
       </c>
       <c r="M77" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="N77">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="O77" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P77" t="s">
         <v>26</v>
       </c>
       <c r="Q77" t="s">
-        <v>30</v>
+        <v>88</v>
       </c>
       <c r="R77" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="S77">
         <v>30.458388</v>
@@ -6552,16 +6513,16 @@
         <v>74.453514</v>
       </c>
       <c r="U77" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="V77">
-        <v>20480</v>
+        <v>15353</v>
       </c>
       <c r="W77" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="X77" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
     </row>
     <row r="78" spans="1:24">
@@ -6578,46 +6539,46 @@
         <v>30</v>
       </c>
       <c r="E78" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F78">
-        <v>1323</v>
+        <v>1607</v>
       </c>
       <c r="G78" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H78">
-        <v>30.61296</v>
+        <v>30.4726737</v>
       </c>
       <c r="I78">
-        <v>75.84106</v>
+        <v>74.5049465</v>
       </c>
       <c r="J78">
-        <v>999</v>
+        <v>1512</v>
       </c>
       <c r="K78">
-        <v>30.561546</v>
+        <v>30.4713293</v>
       </c>
       <c r="L78">
-        <v>75.352118</v>
+        <v>74.5033904</v>
       </c>
       <c r="M78" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="N78">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="O78" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P78" t="s">
         <v>26</v>
       </c>
       <c r="Q78" t="s">
-        <v>30</v>
+        <v>88</v>
       </c>
       <c r="R78" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="S78">
         <v>30.458388</v>
@@ -6626,16 +6587,16 @@
         <v>74.453514</v>
       </c>
       <c r="U78" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="V78">
-        <v>18000</v>
+        <v>20480</v>
       </c>
       <c r="W78" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="X78" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
     </row>
     <row r="79" spans="1:24">
@@ -6652,46 +6613,46 @@
         <v>30</v>
       </c>
       <c r="E79" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F79">
-        <v>1324</v>
+        <v>1607</v>
       </c>
       <c r="G79" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="H79">
-        <v>30.59296</v>
+        <v>30.4726737</v>
       </c>
       <c r="I79">
-        <v>75.78903</v>
+        <v>74.5049465</v>
       </c>
       <c r="J79">
-        <v>216</v>
+        <v>1512</v>
       </c>
       <c r="K79">
-        <v>30.5076194</v>
+        <v>30.4713293</v>
       </c>
       <c r="L79">
-        <v>74.958715</v>
+        <v>74.5033904</v>
       </c>
       <c r="M79" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="N79">
-        <v>864</v>
+        <v>879</v>
       </c>
       <c r="O79" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P79" t="s">
         <v>26</v>
       </c>
       <c r="Q79" t="s">
-        <v>30</v>
+        <v>88</v>
       </c>
       <c r="R79" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="S79">
         <v>30.458388</v>
@@ -6700,16 +6661,16 @@
         <v>74.453514</v>
       </c>
       <c r="U79" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="V79">
-        <v>41830</v>
+        <v>20480</v>
       </c>
       <c r="W79" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="X79" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
     </row>
     <row r="80" spans="1:24">
@@ -6726,46 +6687,46 @@
         <v>30</v>
       </c>
       <c r="E80" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F80">
-        <v>1325</v>
+        <v>1607</v>
       </c>
       <c r="G80" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="H80">
-        <v>30.61907</v>
+        <v>30.4726737</v>
       </c>
       <c r="I80">
-        <v>75.8098</v>
+        <v>74.5049465</v>
       </c>
       <c r="J80">
-        <v>217</v>
+        <v>1512</v>
       </c>
       <c r="K80">
-        <v>30.51445</v>
+        <v>30.4713293</v>
       </c>
       <c r="L80">
-        <v>74.89836</v>
+        <v>74.5033904</v>
       </c>
       <c r="M80" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="N80">
-        <v>864</v>
+        <v>880</v>
       </c>
       <c r="O80" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P80" t="s">
         <v>26</v>
       </c>
       <c r="Q80" t="s">
-        <v>30</v>
+        <v>88</v>
       </c>
       <c r="R80" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="S80">
         <v>30.458388</v>
@@ -6774,16 +6735,16 @@
         <v>74.453514</v>
       </c>
       <c r="U80" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="V80">
-        <v>55220</v>
+        <v>15360</v>
       </c>
       <c r="W80" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="X80" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
     </row>
     <row r="81" spans="1:24">
@@ -6800,64 +6761,64 @@
         <v>30</v>
       </c>
       <c r="E81" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F81">
-        <v>1326</v>
+        <v>1660</v>
       </c>
       <c r="G81" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="H81">
-        <v>30.60582</v>
+        <v>30.2397029</v>
       </c>
       <c r="I81">
-        <v>75.87558</v>
+        <v>74.2953411</v>
       </c>
       <c r="J81">
-        <v>57</v>
+        <v>279</v>
       </c>
       <c r="K81">
-        <v>30.58822</v>
+        <v>30.175344</v>
       </c>
       <c r="L81">
-        <v>75.6722</v>
+        <v>74.178363</v>
       </c>
       <c r="M81" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="N81">
-        <v>866</v>
+        <v>401</v>
       </c>
       <c r="O81" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P81" t="s">
         <v>26</v>
       </c>
       <c r="Q81" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="R81" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="S81">
-        <v>30.458388</v>
+        <v>30.17081207</v>
       </c>
       <c r="T81">
-        <v>74.453514</v>
+        <v>74.18179719</v>
       </c>
       <c r="U81" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="V81">
-        <v>13140</v>
+        <v>1314.5</v>
       </c>
       <c r="W81" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="X81" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
     </row>
     <row r="82" spans="1:24">
@@ -6874,64 +6835,64 @@
         <v>30</v>
       </c>
       <c r="E82" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F82">
-        <v>1326</v>
+        <v>1660</v>
       </c>
       <c r="G82" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="H82">
-        <v>30.60582</v>
+        <v>30.2397029</v>
       </c>
       <c r="I82">
-        <v>75.87558</v>
+        <v>74.2953411</v>
       </c>
       <c r="J82">
-        <v>57</v>
+        <v>279</v>
       </c>
       <c r="K82">
-        <v>30.58822</v>
+        <v>30.175344</v>
       </c>
       <c r="L82">
-        <v>75.6722</v>
+        <v>74.178363</v>
       </c>
       <c r="M82" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="N82">
-        <v>874</v>
+        <v>406</v>
       </c>
       <c r="O82" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P82" t="s">
         <v>26</v>
       </c>
       <c r="Q82" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="R82" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="S82">
-        <v>30.458388</v>
+        <v>30.16991135</v>
       </c>
       <c r="T82">
-        <v>74.453514</v>
+        <v>74.18230296</v>
       </c>
       <c r="U82" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="V82">
-        <v>28460</v>
+        <v>52394.5</v>
       </c>
       <c r="W82" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="X82" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
     </row>
     <row r="83" spans="1:24">
@@ -6945,67 +6906,67 @@
         <v>26</v>
       </c>
       <c r="D83" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E83" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F83">
-        <v>1326</v>
+        <v>2153</v>
       </c>
       <c r="G83" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="H83">
-        <v>30.60582</v>
+        <v>31.3953454</v>
       </c>
       <c r="I83">
-        <v>75.87558</v>
+        <v>74.6222925</v>
       </c>
       <c r="J83">
-        <v>57</v>
+        <v>1948</v>
       </c>
       <c r="K83">
-        <v>30.58822</v>
+        <v>31.361236</v>
       </c>
       <c r="L83">
-        <v>75.6722</v>
+        <v>74.66727400000001</v>
       </c>
       <c r="M83" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="N83">
-        <v>879</v>
+        <v>2</v>
       </c>
       <c r="O83" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P83" t="s">
         <v>26</v>
       </c>
       <c r="Q83" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="R83" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="S83">
-        <v>30.458388</v>
+        <v>31.45335</v>
       </c>
       <c r="T83">
-        <v>74.453514</v>
+        <v>74.46541999999999</v>
       </c>
       <c r="U83" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="V83">
-        <v>2480</v>
+        <v>150000</v>
       </c>
       <c r="W83" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="X83" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
     </row>
     <row r="84" spans="1:24">
@@ -7019,437 +6980,67 @@
         <v>26</v>
       </c>
       <c r="D84" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E84" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F84">
-        <v>1327</v>
+        <v>2153</v>
       </c>
       <c r="G84" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="H84">
-        <v>30.62411</v>
+        <v>31.3953454</v>
       </c>
       <c r="I84">
-        <v>75.75073</v>
+        <v>74.6222925</v>
       </c>
       <c r="J84">
-        <v>217</v>
+        <v>1948</v>
       </c>
       <c r="K84">
-        <v>30.51445</v>
+        <v>31.361236</v>
       </c>
       <c r="L84">
-        <v>74.89836</v>
+        <v>74.66727400000001</v>
       </c>
       <c r="M84" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="N84">
-        <v>866</v>
+        <v>4</v>
       </c>
       <c r="O84" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P84" t="s">
         <v>26</v>
       </c>
       <c r="Q84" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="R84" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="S84">
-        <v>30.458388</v>
+        <v>31.45335</v>
       </c>
       <c r="T84">
-        <v>74.453514</v>
+        <v>74.46541999999999</v>
       </c>
       <c r="U84" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="V84">
-        <v>59240</v>
+        <v>150000</v>
       </c>
       <c r="W84" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="X84" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="85" spans="1:24">
-      <c r="A85" t="s">
-        <v>24</v>
-      </c>
-      <c r="B85" t="s">
-        <v>25</v>
-      </c>
-      <c r="C85" t="s">
-        <v>26</v>
-      </c>
-      <c r="D85" t="s">
-        <v>30</v>
-      </c>
-      <c r="E85" t="s">
-        <v>34</v>
-      </c>
-      <c r="F85">
-        <v>1328</v>
-      </c>
-      <c r="G85" t="s">
-        <v>90</v>
-      </c>
-      <c r="H85">
-        <v>30.58776</v>
-      </c>
-      <c r="I85">
-        <v>75.81787</v>
-      </c>
-      <c r="J85">
-        <v>216</v>
-      </c>
-      <c r="K85">
-        <v>30.5076194</v>
-      </c>
-      <c r="L85">
-        <v>74.958715</v>
-      </c>
-      <c r="M85" t="s">
-        <v>94</v>
-      </c>
-      <c r="N85">
-        <v>866</v>
-      </c>
-      <c r="O85" t="s">
-        <v>95</v>
-      </c>
-      <c r="P85" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q85" t="s">
-        <v>30</v>
-      </c>
-      <c r="R85" t="s">
-        <v>34</v>
-      </c>
-      <c r="S85">
-        <v>30.458388</v>
-      </c>
-      <c r="T85">
-        <v>74.453514</v>
-      </c>
-      <c r="U85" t="s">
-        <v>96</v>
-      </c>
-      <c r="V85">
-        <v>11670</v>
-      </c>
-      <c r="W85" t="s">
-        <v>159</v>
-      </c>
-      <c r="X85" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="86" spans="1:24">
-      <c r="A86" t="s">
-        <v>24</v>
-      </c>
-      <c r="B86" t="s">
-        <v>25</v>
-      </c>
-      <c r="C86" t="s">
-        <v>26</v>
-      </c>
-      <c r="D86" t="s">
-        <v>30</v>
-      </c>
-      <c r="E86" t="s">
-        <v>34</v>
-      </c>
-      <c r="F86">
-        <v>1328</v>
-      </c>
-      <c r="G86" t="s">
-        <v>90</v>
-      </c>
-      <c r="H86">
-        <v>30.58776</v>
-      </c>
-      <c r="I86">
-        <v>75.81787</v>
-      </c>
-      <c r="J86">
-        <v>216</v>
-      </c>
-      <c r="K86">
-        <v>30.5076194</v>
-      </c>
-      <c r="L86">
-        <v>74.958715</v>
-      </c>
-      <c r="M86" t="s">
-        <v>94</v>
-      </c>
-      <c r="N86">
-        <v>880</v>
-      </c>
-      <c r="O86" t="s">
-        <v>95</v>
-      </c>
-      <c r="P86" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q86" t="s">
-        <v>30</v>
-      </c>
-      <c r="R86" t="s">
-        <v>34</v>
-      </c>
-      <c r="S86">
-        <v>30.458388</v>
-      </c>
-      <c r="T86">
-        <v>74.453514</v>
-      </c>
-      <c r="U86" t="s">
-        <v>96</v>
-      </c>
-      <c r="V86">
-        <v>15360</v>
-      </c>
-      <c r="W86" t="s">
-        <v>159</v>
-      </c>
-      <c r="X86" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="87" spans="1:24">
-      <c r="A87" t="s">
-        <v>24</v>
-      </c>
-      <c r="B87" t="s">
-        <v>25</v>
-      </c>
-      <c r="C87" t="s">
-        <v>26</v>
-      </c>
-      <c r="D87" t="s">
-        <v>30</v>
-      </c>
-      <c r="E87" t="s">
-        <v>34</v>
-      </c>
-      <c r="F87">
-        <v>1329</v>
-      </c>
-      <c r="G87" t="s">
-        <v>91</v>
-      </c>
-      <c r="H87">
-        <v>30.669134</v>
-      </c>
-      <c r="I87">
-        <v>75.877723</v>
-      </c>
-      <c r="J87">
-        <v>678</v>
-      </c>
-      <c r="K87">
-        <v>30.633572</v>
-      </c>
-      <c r="L87">
-        <v>75.628421</v>
-      </c>
-      <c r="M87" t="s">
-        <v>94</v>
-      </c>
-      <c r="N87">
-        <v>877</v>
-      </c>
-      <c r="O87" t="s">
-        <v>95</v>
-      </c>
-      <c r="P87" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q87" t="s">
-        <v>30</v>
-      </c>
-      <c r="R87" t="s">
-        <v>34</v>
-      </c>
-      <c r="S87">
-        <v>30.458388</v>
-      </c>
-      <c r="T87">
-        <v>74.453514</v>
-      </c>
-      <c r="U87" t="s">
-        <v>96</v>
-      </c>
-      <c r="V87">
-        <v>10530</v>
-      </c>
-      <c r="W87" t="s">
-        <v>160</v>
-      </c>
-      <c r="X87" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="88" spans="1:24">
-      <c r="A88" t="s">
-        <v>24</v>
-      </c>
-      <c r="B88" t="s">
-        <v>25</v>
-      </c>
-      <c r="C88" t="s">
-        <v>26</v>
-      </c>
-      <c r="D88" t="s">
-        <v>30</v>
-      </c>
-      <c r="E88" t="s">
-        <v>34</v>
-      </c>
-      <c r="F88">
-        <v>1330</v>
-      </c>
-      <c r="G88" t="s">
-        <v>92</v>
-      </c>
-      <c r="H88">
-        <v>30.651445</v>
-      </c>
-      <c r="I88">
-        <v>75.890028</v>
-      </c>
-      <c r="J88">
-        <v>1225</v>
-      </c>
-      <c r="K88">
-        <v>30.5792101</v>
-      </c>
-      <c r="L88">
-        <v>75.30097960000001</v>
-      </c>
-      <c r="M88" t="s">
-        <v>94</v>
-      </c>
-      <c r="N88">
-        <v>872</v>
-      </c>
-      <c r="O88" t="s">
-        <v>95</v>
-      </c>
-      <c r="P88" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q88" t="s">
-        <v>30</v>
-      </c>
-      <c r="R88" t="s">
-        <v>34</v>
-      </c>
-      <c r="S88">
-        <v>30.458388</v>
-      </c>
-      <c r="T88">
-        <v>74.453514</v>
-      </c>
-      <c r="U88" t="s">
-        <v>96</v>
-      </c>
-      <c r="V88">
-        <v>29640</v>
-      </c>
-      <c r="W88" t="s">
-        <v>161</v>
-      </c>
-      <c r="X88" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="89" spans="1:24">
-      <c r="A89" t="s">
-        <v>24</v>
-      </c>
-      <c r="B89" t="s">
-        <v>25</v>
-      </c>
-      <c r="C89" t="s">
-        <v>27</v>
-      </c>
-      <c r="D89" t="s">
-        <v>31</v>
-      </c>
-      <c r="E89" t="s">
-        <v>35</v>
-      </c>
-      <c r="F89">
-        <v>1660</v>
-      </c>
-      <c r="G89" t="s">
-        <v>93</v>
-      </c>
-      <c r="H89">
-        <v>30.2397029</v>
-      </c>
-      <c r="I89">
-        <v>74.2953411</v>
-      </c>
-      <c r="J89">
-        <v>287</v>
-      </c>
-      <c r="K89">
-        <v>30.126927</v>
-      </c>
-      <c r="L89">
-        <v>74.161942</v>
-      </c>
-      <c r="M89" t="s">
-        <v>94</v>
-      </c>
-      <c r="N89">
-        <v>407</v>
-      </c>
-      <c r="O89" t="s">
-        <v>95</v>
-      </c>
-      <c r="P89" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q89" t="s">
-        <v>29</v>
-      </c>
-      <c r="R89" t="s">
-        <v>33</v>
-      </c>
-      <c r="S89">
-        <v>30.126927</v>
-      </c>
-      <c r="T89">
-        <v>74.161942</v>
-      </c>
-      <c r="U89" t="s">
-        <v>96</v>
-      </c>
-      <c r="V89">
-        <v>15621</v>
-      </c>
-      <c r="W89" t="s">
-        <v>162</v>
-      </c>
-      <c r="X89" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
     </row>
   </sheetData>

--- a/pds_admin_Punjab_R/Backend/Backend/Result_Sheet12_F1.xlsx
+++ b/pds_admin_Punjab_R/Backend/Backend/Result_Sheet12_F1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1186" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1186" uniqueCount="154">
   <si>
     <t>Scenario</t>
   </si>
@@ -280,7 +280,16 @@
     <t>agah</t>
   </si>
   <si>
-    <t>MALERKOTLA</t>
+    <t>Amritsar</t>
+  </si>
+  <si>
+    <t>Fazilka</t>
+  </si>
+  <si>
+    <t>Jalandhar</t>
+  </si>
+  <si>
+    <t>Malerkotla</t>
   </si>
   <si>
     <t>Paddy</t>
@@ -951,7 +960,7 @@
         <v>26</v>
       </c>
       <c r="Q2" t="s">
-        <v>27</v>
+        <v>88</v>
       </c>
       <c r="R2" t="s">
         <v>32</v>
@@ -963,16 +972,16 @@
         <v>74.91584450000001</v>
       </c>
       <c r="U2" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="V2">
         <v>50000</v>
       </c>
       <c r="W2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="X2" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="3" spans="1:24">
@@ -1025,7 +1034,7 @@
         <v>26</v>
       </c>
       <c r="Q3" t="s">
-        <v>27</v>
+        <v>88</v>
       </c>
       <c r="R3" t="s">
         <v>32</v>
@@ -1037,16 +1046,16 @@
         <v>74.588493</v>
       </c>
       <c r="U3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="V3">
         <v>50000</v>
       </c>
       <c r="W3" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="X3" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="4" spans="1:24">
@@ -1099,7 +1108,7 @@
         <v>26</v>
       </c>
       <c r="Q4" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="R4" t="s">
         <v>32</v>
@@ -1111,16 +1120,16 @@
         <v>74.18214294000001</v>
       </c>
       <c r="U4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="V4">
         <v>90000</v>
       </c>
       <c r="W4" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="X4" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="5" spans="1:24">
@@ -1173,7 +1182,7 @@
         <v>26</v>
       </c>
       <c r="Q5" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="R5" t="s">
         <v>32</v>
@@ -1185,16 +1194,16 @@
         <v>74.18094151</v>
       </c>
       <c r="U5" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="V5">
         <v>60000</v>
       </c>
       <c r="W5" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="X5" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="6" spans="1:24">
@@ -1247,7 +1256,7 @@
         <v>26</v>
       </c>
       <c r="Q6" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="R6" t="s">
         <v>32</v>
@@ -1259,16 +1268,16 @@
         <v>74.18085842000001</v>
       </c>
       <c r="U6" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="V6">
         <v>120000</v>
       </c>
       <c r="W6" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="X6" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="7" spans="1:24">
@@ -1321,7 +1330,7 @@
         <v>26</v>
       </c>
       <c r="Q7" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="R7" t="s">
         <v>32</v>
@@ -1333,16 +1342,16 @@
         <v>74.16401603</v>
       </c>
       <c r="U7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="V7">
         <v>33610</v>
       </c>
       <c r="W7" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="X7" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="8" spans="1:24">
@@ -1395,7 +1404,7 @@
         <v>26</v>
       </c>
       <c r="Q8" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="R8" t="s">
         <v>32</v>
@@ -1407,16 +1416,16 @@
         <v>74.18315728</v>
       </c>
       <c r="U8" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="V8">
         <v>150000</v>
       </c>
       <c r="W8" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="X8" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="9" spans="1:24">
@@ -1469,7 +1478,7 @@
         <v>26</v>
       </c>
       <c r="Q9" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="R9" t="s">
         <v>32</v>
@@ -1481,16 +1490,16 @@
         <v>74.161942</v>
       </c>
       <c r="U9" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="V9">
         <v>143264</v>
       </c>
       <c r="W9" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="X9" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="10" spans="1:24">
@@ -1543,7 +1552,7 @@
         <v>26</v>
       </c>
       <c r="Q10" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="R10" t="s">
         <v>32</v>
@@ -1555,16 +1564,16 @@
         <v>74.20908439</v>
       </c>
       <c r="U10" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="V10">
         <v>48247.5</v>
       </c>
       <c r="W10" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="X10" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="11" spans="1:24">
@@ -1617,7 +1626,7 @@
         <v>26</v>
       </c>
       <c r="Q11" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="R11" t="s">
         <v>32</v>
@@ -1629,16 +1638,16 @@
         <v>74.206666</v>
       </c>
       <c r="U11" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="V11">
         <v>23588</v>
       </c>
       <c r="W11" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="X11" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="12" spans="1:24">
@@ -1691,7 +1700,7 @@
         <v>26</v>
       </c>
       <c r="Q12" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="R12" t="s">
         <v>32</v>
@@ -1703,16 +1712,16 @@
         <v>74.18014506</v>
       </c>
       <c r="U12" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="V12">
         <v>73860.5</v>
       </c>
       <c r="W12" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="X12" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="13" spans="1:24">
@@ -1765,7 +1774,7 @@
         <v>26</v>
       </c>
       <c r="Q13" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="R13" t="s">
         <v>32</v>
@@ -1777,16 +1786,16 @@
         <v>74.161942</v>
       </c>
       <c r="U13" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="V13">
         <v>37309</v>
       </c>
       <c r="W13" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="X13" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="14" spans="1:24">
@@ -1839,7 +1848,7 @@
         <v>26</v>
       </c>
       <c r="Q14" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="R14" t="s">
         <v>32</v>
@@ -1851,16 +1860,16 @@
         <v>74.161942</v>
       </c>
       <c r="U14" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="V14">
         <v>18025.5</v>
       </c>
       <c r="W14" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="X14" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="15" spans="1:24">
@@ -1913,7 +1922,7 @@
         <v>26</v>
       </c>
       <c r="Q15" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="R15" t="s">
         <v>32</v>
@@ -1925,16 +1934,16 @@
         <v>74.20908439</v>
       </c>
       <c r="U15" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="V15">
         <v>16177.5</v>
       </c>
       <c r="W15" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="X15" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="16" spans="1:24">
@@ -1987,7 +1996,7 @@
         <v>26</v>
       </c>
       <c r="Q16" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="R16" t="s">
         <v>32</v>
@@ -1999,16 +2008,16 @@
         <v>74.20888524</v>
       </c>
       <c r="U16" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="V16">
         <v>33588.5</v>
       </c>
       <c r="W16" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="X16" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="17" spans="1:24">
@@ -2061,7 +2070,7 @@
         <v>26</v>
       </c>
       <c r="Q17" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="R17" t="s">
         <v>32</v>
@@ -2073,16 +2082,16 @@
         <v>74.183232</v>
       </c>
       <c r="U17" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="V17">
         <v>13129</v>
       </c>
       <c r="W17" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="X17" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="18" spans="1:24">
@@ -2135,7 +2144,7 @@
         <v>26</v>
       </c>
       <c r="Q18" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="R18" t="s">
         <v>32</v>
@@ -2147,16 +2156,16 @@
         <v>74.161942</v>
       </c>
       <c r="U18" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="V18">
         <v>28578.5</v>
       </c>
       <c r="W18" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="X18" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="19" spans="1:24">
@@ -2209,7 +2218,7 @@
         <v>26</v>
       </c>
       <c r="Q19" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="R19" t="s">
         <v>32</v>
@@ -2221,16 +2230,16 @@
         <v>74.16401603</v>
       </c>
       <c r="U19" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="V19">
         <v>18038</v>
       </c>
       <c r="W19" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="X19" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="20" spans="1:24">
@@ -2283,7 +2292,7 @@
         <v>26</v>
       </c>
       <c r="Q20" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="R20" t="s">
         <v>32</v>
@@ -2295,16 +2304,16 @@
         <v>74.161942</v>
       </c>
       <c r="U20" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="V20">
         <v>44568.5</v>
       </c>
       <c r="W20" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="X20" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="21" spans="1:24">
@@ -2357,7 +2366,7 @@
         <v>26</v>
       </c>
       <c r="Q21" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="R21" t="s">
         <v>32</v>
@@ -2369,16 +2378,16 @@
         <v>74.206666</v>
       </c>
       <c r="U21" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="V21">
         <v>25216</v>
       </c>
       <c r="W21" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="X21" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="22" spans="1:24">
@@ -2431,7 +2440,7 @@
         <v>26</v>
       </c>
       <c r="Q22" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="R22" t="s">
         <v>32</v>
@@ -2443,16 +2452,16 @@
         <v>74.18179719</v>
       </c>
       <c r="U22" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="V22">
         <v>44802</v>
       </c>
       <c r="W22" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="X22" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="23" spans="1:24">
@@ -2505,7 +2514,7 @@
         <v>26</v>
       </c>
       <c r="Q23" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="R23" t="s">
         <v>32</v>
@@ -2517,16 +2526,16 @@
         <v>74.161942</v>
       </c>
       <c r="U23" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="V23">
         <v>30276.5</v>
       </c>
       <c r="W23" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="X23" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="24" spans="1:24">
@@ -2579,7 +2588,7 @@
         <v>26</v>
       </c>
       <c r="Q24" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="R24" t="s">
         <v>32</v>
@@ -2591,16 +2600,16 @@
         <v>74.20888524</v>
       </c>
       <c r="U24" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="V24">
         <v>19961.5</v>
       </c>
       <c r="W24" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="X24" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="25" spans="1:24">
@@ -2653,7 +2662,7 @@
         <v>26</v>
       </c>
       <c r="Q25" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="R25" t="s">
         <v>32</v>
@@ -2665,16 +2674,16 @@
         <v>74.20908439</v>
       </c>
       <c r="U25" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="V25">
         <v>64381</v>
       </c>
       <c r="W25" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="X25" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="26" spans="1:24">
@@ -2727,7 +2736,7 @@
         <v>26</v>
       </c>
       <c r="Q26" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="R26" t="s">
         <v>32</v>
@@ -2739,16 +2748,16 @@
         <v>74.16401603</v>
       </c>
       <c r="U26" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="V26">
         <v>39817.5</v>
       </c>
       <c r="W26" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="X26" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="27" spans="1:24">
@@ -2801,7 +2810,7 @@
         <v>26</v>
       </c>
       <c r="Q27" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="R27" t="s">
         <v>32</v>
@@ -2813,16 +2822,16 @@
         <v>74.183232</v>
       </c>
       <c r="U27" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="V27">
         <v>10375.5</v>
       </c>
       <c r="W27" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="X27" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="28" spans="1:24">
@@ -2875,7 +2884,7 @@
         <v>26</v>
       </c>
       <c r="Q28" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="R28" t="s">
         <v>32</v>
@@ -2887,16 +2896,16 @@
         <v>74.161942</v>
       </c>
       <c r="U28" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="V28">
         <v>100949.5</v>
       </c>
       <c r="W28" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="X28" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="29" spans="1:24">
@@ -2949,7 +2958,7 @@
         <v>26</v>
       </c>
       <c r="Q29" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="R29" t="s">
         <v>32</v>
@@ -2961,16 +2970,16 @@
         <v>74.17723581</v>
       </c>
       <c r="U29" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="V29">
         <v>36622.5</v>
       </c>
       <c r="W29" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="X29" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="30" spans="1:24">
@@ -3023,7 +3032,7 @@
         <v>26</v>
       </c>
       <c r="Q30" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="R30" t="s">
         <v>32</v>
@@ -3035,16 +3044,16 @@
         <v>74.18014506</v>
       </c>
       <c r="U30" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="V30">
         <v>11652.5</v>
       </c>
       <c r="W30" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="X30" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="31" spans="1:24">
@@ -3097,7 +3106,7 @@
         <v>26</v>
       </c>
       <c r="Q31" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="R31" t="s">
         <v>32</v>
@@ -3109,16 +3118,16 @@
         <v>74.161942</v>
       </c>
       <c r="U31" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="V31">
         <v>16592.5</v>
       </c>
       <c r="W31" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="X31" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="32" spans="1:24">
@@ -3171,7 +3180,7 @@
         <v>26</v>
       </c>
       <c r="Q32" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="R32" t="s">
         <v>32</v>
@@ -3183,16 +3192,16 @@
         <v>74.161942</v>
       </c>
       <c r="U32" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="V32">
         <v>21311</v>
       </c>
       <c r="W32" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="X32" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="33" spans="1:24">
@@ -3245,7 +3254,7 @@
         <v>26</v>
       </c>
       <c r="Q33" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="R33" t="s">
         <v>32</v>
@@ -3257,16 +3266,16 @@
         <v>74.20908439</v>
       </c>
       <c r="U33" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="V33">
         <v>34094</v>
       </c>
       <c r="W33" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="X33" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="34" spans="1:24">
@@ -3319,7 +3328,7 @@
         <v>26</v>
       </c>
       <c r="Q34" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="R34" t="s">
         <v>32</v>
@@ -3331,16 +3340,16 @@
         <v>74.183232</v>
       </c>
       <c r="U34" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="V34">
         <v>10795.5</v>
       </c>
       <c r="W34" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="X34" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="35" spans="1:24">
@@ -3393,7 +3402,7 @@
         <v>26</v>
       </c>
       <c r="Q35" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="R35" t="s">
         <v>32</v>
@@ -3405,16 +3414,16 @@
         <v>74.18230296</v>
       </c>
       <c r="U35" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="V35">
         <v>21605.5</v>
       </c>
       <c r="W35" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="X35" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="36" spans="1:24">
@@ -3467,7 +3476,7 @@
         <v>26</v>
       </c>
       <c r="Q36" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="R36" t="s">
         <v>32</v>
@@ -3479,16 +3488,16 @@
         <v>74.206666</v>
       </c>
       <c r="U36" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="V36">
         <v>71196</v>
       </c>
       <c r="W36" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="X36" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="37" spans="1:24">
@@ -3541,7 +3550,7 @@
         <v>26</v>
       </c>
       <c r="Q37" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="R37" t="s">
         <v>32</v>
@@ -3553,16 +3562,16 @@
         <v>74.161942</v>
       </c>
       <c r="U37" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="V37">
         <v>2489</v>
       </c>
       <c r="W37" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="X37" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="38" spans="1:24">
@@ -3615,7 +3624,7 @@
         <v>26</v>
       </c>
       <c r="Q38" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="R38" t="s">
         <v>32</v>
@@ -3627,16 +3636,16 @@
         <v>74.161942</v>
       </c>
       <c r="U38" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="V38">
         <v>34208</v>
       </c>
       <c r="W38" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="X38" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="39" spans="1:24">
@@ -3689,7 +3698,7 @@
         <v>26</v>
       </c>
       <c r="Q39" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="R39" t="s">
         <v>32</v>
@@ -3701,16 +3710,16 @@
         <v>74.16401603</v>
       </c>
       <c r="U39" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="V39">
         <v>54819.5</v>
       </c>
       <c r="W39" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="X39" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="40" spans="1:24">
@@ -3763,7 +3772,7 @@
         <v>26</v>
       </c>
       <c r="Q40" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="R40" t="s">
         <v>32</v>
@@ -3775,16 +3784,16 @@
         <v>74.161942</v>
       </c>
       <c r="U40" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="V40">
         <v>37768</v>
       </c>
       <c r="W40" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="X40" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="41" spans="1:24">
@@ -3837,7 +3846,7 @@
         <v>26</v>
       </c>
       <c r="Q41" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="R41" t="s">
         <v>32</v>
@@ -3849,16 +3858,16 @@
         <v>74.161942</v>
       </c>
       <c r="U41" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="V41">
         <v>29874.5</v>
       </c>
       <c r="W41" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="X41" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="42" spans="1:24">
@@ -3911,7 +3920,7 @@
         <v>26</v>
       </c>
       <c r="Q42" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="R42" t="s">
         <v>32</v>
@@ -3923,16 +3932,16 @@
         <v>74.161942</v>
       </c>
       <c r="U42" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="V42">
         <v>56983.5</v>
       </c>
       <c r="W42" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="X42" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="43" spans="1:24">
@@ -3985,7 +3994,7 @@
         <v>26</v>
       </c>
       <c r="Q43" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="R43" t="s">
         <v>32</v>
@@ -3997,16 +4006,16 @@
         <v>74.161942</v>
       </c>
       <c r="U43" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="V43">
         <v>23195.5</v>
       </c>
       <c r="W43" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="X43" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="44" spans="1:24">
@@ -4059,7 +4068,7 @@
         <v>26</v>
       </c>
       <c r="Q44" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="R44" t="s">
         <v>32</v>
@@ -4071,16 +4080,16 @@
         <v>74.161942</v>
       </c>
       <c r="U44" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="V44">
         <v>57368</v>
       </c>
       <c r="W44" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="X44" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="45" spans="1:24">
@@ -4133,7 +4142,7 @@
         <v>26</v>
       </c>
       <c r="Q45" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="R45" t="s">
         <v>32</v>
@@ -4145,16 +4154,16 @@
         <v>74.18014506</v>
       </c>
       <c r="U45" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="V45">
         <v>2487</v>
       </c>
       <c r="W45" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="X45" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="46" spans="1:24">
@@ -4207,7 +4216,7 @@
         <v>26</v>
       </c>
       <c r="Q46" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="R46" t="s">
         <v>32</v>
@@ -4219,16 +4228,16 @@
         <v>74.16401603</v>
       </c>
       <c r="U46" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="V46">
         <v>29195</v>
       </c>
       <c r="W46" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="X46" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="47" spans="1:24">
@@ -4281,7 +4290,7 @@
         <v>26</v>
       </c>
       <c r="Q47" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="R47" t="s">
         <v>32</v>
@@ -4293,16 +4302,16 @@
         <v>74.16401603</v>
       </c>
       <c r="U47" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="V47">
         <v>26795</v>
       </c>
       <c r="W47" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="X47" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="48" spans="1:24">
@@ -4355,7 +4364,7 @@
         <v>26</v>
       </c>
       <c r="Q48" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="R48" t="s">
         <v>32</v>
@@ -4367,16 +4376,16 @@
         <v>74.16401603</v>
       </c>
       <c r="U48" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="V48">
         <v>7950</v>
       </c>
       <c r="W48" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="X48" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="49" spans="1:24">
@@ -4429,7 +4438,7 @@
         <v>26</v>
       </c>
       <c r="Q49" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="R49" t="s">
         <v>32</v>
@@ -4441,16 +4450,16 @@
         <v>74.18014506</v>
       </c>
       <c r="U49" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="V49">
         <v>5500</v>
       </c>
       <c r="W49" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="X49" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="50" spans="1:24">
@@ -4503,7 +4512,7 @@
         <v>26</v>
       </c>
       <c r="Q50" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="R50" t="s">
         <v>32</v>
@@ -4515,16 +4524,16 @@
         <v>74.161942</v>
       </c>
       <c r="U50" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="V50">
         <v>12630.5</v>
       </c>
       <c r="W50" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="X50" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="51" spans="1:24">
@@ -4577,7 +4586,7 @@
         <v>26</v>
       </c>
       <c r="Q51" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="R51" t="s">
         <v>32</v>
@@ -4589,16 +4598,16 @@
         <v>74.161942</v>
       </c>
       <c r="U51" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="V51">
         <v>13803</v>
       </c>
       <c r="W51" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="X51" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="52" spans="1:24">
@@ -4651,7 +4660,7 @@
         <v>26</v>
       </c>
       <c r="Q52" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="R52" t="s">
         <v>32</v>
@@ -4663,16 +4672,16 @@
         <v>74.161942</v>
       </c>
       <c r="U52" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="V52">
         <v>9145</v>
       </c>
       <c r="W52" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="X52" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="53" spans="1:24">
@@ -4725,7 +4734,7 @@
         <v>26</v>
       </c>
       <c r="Q53" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="R53" t="s">
         <v>32</v>
@@ -4737,16 +4746,16 @@
         <v>74.18179719</v>
       </c>
       <c r="U53" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="V53">
         <v>17622.5</v>
       </c>
       <c r="W53" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="X53" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="54" spans="1:24">
@@ -4799,7 +4808,7 @@
         <v>26</v>
       </c>
       <c r="Q54" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="R54" t="s">
         <v>32</v>
@@ -4811,16 +4820,16 @@
         <v>74.16401603</v>
       </c>
       <c r="U54" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="V54">
         <v>2347.5</v>
       </c>
       <c r="W54" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="X54" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="55" spans="1:24">
@@ -4873,7 +4882,7 @@
         <v>26</v>
       </c>
       <c r="Q55" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="R55" t="s">
         <v>32</v>
@@ -4885,16 +4894,16 @@
         <v>74.17723581</v>
       </c>
       <c r="U55" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="V55">
         <v>40337.5</v>
       </c>
       <c r="W55" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="X55" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="56" spans="1:24">
@@ -4947,7 +4956,7 @@
         <v>26</v>
       </c>
       <c r="Q56" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="R56" t="s">
         <v>32</v>
@@ -4959,16 +4968,16 @@
         <v>74.18179719</v>
       </c>
       <c r="U56" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="V56">
         <v>56502.5</v>
       </c>
       <c r="W56" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="X56" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="57" spans="1:24">
@@ -5021,7 +5030,7 @@
         <v>26</v>
       </c>
       <c r="Q57" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="R57" t="s">
         <v>32</v>
@@ -5033,16 +5042,16 @@
         <v>74.18179719</v>
       </c>
       <c r="U57" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="V57">
         <v>43110</v>
       </c>
       <c r="W57" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="X57" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="58" spans="1:24">
@@ -5095,7 +5104,7 @@
         <v>26</v>
       </c>
       <c r="Q58" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="R58" t="s">
         <v>32</v>
@@ -5107,16 +5116,16 @@
         <v>74.16401603</v>
       </c>
       <c r="U58" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="V58">
         <v>128218</v>
       </c>
       <c r="W58" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="X58" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="59" spans="1:24">
@@ -5169,7 +5178,7 @@
         <v>26</v>
       </c>
       <c r="Q59" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="R59" t="s">
         <v>32</v>
@@ -5181,16 +5190,16 @@
         <v>74.16401603</v>
       </c>
       <c r="U59" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="V59">
         <v>62709.5</v>
       </c>
       <c r="W59" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="X59" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="60" spans="1:24">
@@ -5243,7 +5252,7 @@
         <v>26</v>
       </c>
       <c r="Q60" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="R60" t="s">
         <v>32</v>
@@ -5255,16 +5264,16 @@
         <v>74.18179719</v>
       </c>
       <c r="U60" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="V60">
         <v>47189.5</v>
       </c>
       <c r="W60" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="X60" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="61" spans="1:24">
@@ -5317,7 +5326,7 @@
         <v>26</v>
       </c>
       <c r="Q61" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="R61" t="s">
         <v>32</v>
@@ -5329,16 +5338,16 @@
         <v>75.685958</v>
       </c>
       <c r="U61" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="V61">
         <v>21500</v>
       </c>
       <c r="W61" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="X61" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="62" spans="1:24">
@@ -5391,7 +5400,7 @@
         <v>26</v>
       </c>
       <c r="Q62" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="R62" t="s">
         <v>32</v>
@@ -5403,16 +5412,16 @@
         <v>74.453514</v>
       </c>
       <c r="U62" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="V62">
         <v>88594</v>
       </c>
       <c r="W62" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="X62" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="63" spans="1:24">
@@ -5465,7 +5474,7 @@
         <v>26</v>
       </c>
       <c r="Q63" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="R63" t="s">
         <v>32</v>
@@ -5477,16 +5486,16 @@
         <v>74.453514</v>
       </c>
       <c r="U63" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="V63">
         <v>10000</v>
       </c>
       <c r="W63" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="X63" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="64" spans="1:24">
@@ -5539,7 +5548,7 @@
         <v>26</v>
       </c>
       <c r="Q64" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="R64" t="s">
         <v>32</v>
@@ -5551,16 +5560,16 @@
         <v>74.453514</v>
       </c>
       <c r="U64" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="V64">
         <v>5000</v>
       </c>
       <c r="W64" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="X64" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="65" spans="1:24">
@@ -5613,7 +5622,7 @@
         <v>26</v>
       </c>
       <c r="Q65" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="R65" t="s">
         <v>32</v>
@@ -5625,16 +5634,16 @@
         <v>74.453514</v>
       </c>
       <c r="U65" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="V65">
         <v>5000</v>
       </c>
       <c r="W65" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="X65" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="66" spans="1:24">
@@ -5687,7 +5696,7 @@
         <v>26</v>
       </c>
       <c r="Q66" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="R66" t="s">
         <v>32</v>
@@ -5699,16 +5708,16 @@
         <v>74.453514</v>
       </c>
       <c r="U66" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="V66">
         <v>38086</v>
       </c>
       <c r="W66" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="X66" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="67" spans="1:24">
@@ -5761,7 +5770,7 @@
         <v>26</v>
       </c>
       <c r="Q67" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="R67" t="s">
         <v>32</v>
@@ -5773,16 +5782,16 @@
         <v>74.453514</v>
       </c>
       <c r="U67" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="V67">
         <v>30720</v>
       </c>
       <c r="W67" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="X67" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="68" spans="1:24">
@@ -5835,7 +5844,7 @@
         <v>26</v>
       </c>
       <c r="Q68" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="R68" t="s">
         <v>32</v>
@@ -5847,16 +5856,16 @@
         <v>74.453514</v>
       </c>
       <c r="U68" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="V68">
         <v>5127</v>
       </c>
       <c r="W68" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="X68" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="69" spans="1:24">
@@ -5909,7 +5918,7 @@
         <v>26</v>
       </c>
       <c r="Q69" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="R69" t="s">
         <v>32</v>
@@ -5921,16 +5930,16 @@
         <v>74.453514</v>
       </c>
       <c r="U69" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="V69">
         <v>294680</v>
       </c>
       <c r="W69" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="X69" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="70" spans="1:24">
@@ -5983,7 +5992,7 @@
         <v>26</v>
       </c>
       <c r="Q70" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="R70" t="s">
         <v>32</v>
@@ -5995,16 +6004,16 @@
         <v>74.453514</v>
       </c>
       <c r="U70" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="V70">
         <v>16680</v>
       </c>
       <c r="W70" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="X70" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="71" spans="1:24">
@@ -6057,7 +6066,7 @@
         <v>26</v>
       </c>
       <c r="Q71" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="R71" t="s">
         <v>32</v>
@@ -6069,16 +6078,16 @@
         <v>74.453514</v>
       </c>
       <c r="U71" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="V71">
         <v>10000</v>
       </c>
       <c r="W71" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="X71" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="72" spans="1:24">
@@ -6131,7 +6140,7 @@
         <v>26</v>
       </c>
       <c r="Q72" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="R72" t="s">
         <v>32</v>
@@ -6143,16 +6152,16 @@
         <v>74.453514</v>
       </c>
       <c r="U72" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="V72">
         <v>10000</v>
       </c>
       <c r="W72" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="X72" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="73" spans="1:24">
@@ -6205,7 +6214,7 @@
         <v>26</v>
       </c>
       <c r="Q73" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="R73" t="s">
         <v>32</v>
@@ -6217,16 +6226,16 @@
         <v>74.453514</v>
       </c>
       <c r="U73" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="V73">
         <v>10000</v>
       </c>
       <c r="W73" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="X73" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="74" spans="1:24">
@@ -6279,7 +6288,7 @@
         <v>26</v>
       </c>
       <c r="Q74" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="R74" t="s">
         <v>32</v>
@@ -6291,16 +6300,16 @@
         <v>74.453514</v>
       </c>
       <c r="U74" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="V74">
         <v>30720</v>
       </c>
       <c r="W74" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="X74" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="75" spans="1:24">
@@ -6353,7 +6362,7 @@
         <v>26</v>
       </c>
       <c r="Q75" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="R75" t="s">
         <v>32</v>
@@ -6365,16 +6374,16 @@
         <v>74.453514</v>
       </c>
       <c r="U75" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="V75">
         <v>29640</v>
       </c>
       <c r="W75" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="X75" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="76" spans="1:24">
@@ -6427,7 +6436,7 @@
         <v>26</v>
       </c>
       <c r="Q76" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="R76" t="s">
         <v>32</v>
@@ -6439,16 +6448,16 @@
         <v>74.453514</v>
       </c>
       <c r="U76" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="V76">
         <v>28460</v>
       </c>
       <c r="W76" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="X76" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="77" spans="1:24">
@@ -6501,7 +6510,7 @@
         <v>26</v>
       </c>
       <c r="Q77" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="R77" t="s">
         <v>32</v>
@@ -6513,16 +6522,16 @@
         <v>74.453514</v>
       </c>
       <c r="U77" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="V77">
         <v>15353</v>
       </c>
       <c r="W77" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="X77" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="78" spans="1:24">
@@ -6575,7 +6584,7 @@
         <v>26</v>
       </c>
       <c r="Q78" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="R78" t="s">
         <v>32</v>
@@ -6587,16 +6596,16 @@
         <v>74.453514</v>
       </c>
       <c r="U78" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="V78">
         <v>20480</v>
       </c>
       <c r="W78" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="X78" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="79" spans="1:24">
@@ -6649,7 +6658,7 @@
         <v>26</v>
       </c>
       <c r="Q79" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="R79" t="s">
         <v>32</v>
@@ -6661,16 +6670,16 @@
         <v>74.453514</v>
       </c>
       <c r="U79" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="V79">
         <v>20480</v>
       </c>
       <c r="W79" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="X79" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="80" spans="1:24">
@@ -6723,7 +6732,7 @@
         <v>26</v>
       </c>
       <c r="Q80" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="R80" t="s">
         <v>32</v>
@@ -6735,16 +6744,16 @@
         <v>74.453514</v>
       </c>
       <c r="U80" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="V80">
         <v>15360</v>
       </c>
       <c r="W80" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="X80" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="81" spans="1:24">
@@ -6797,7 +6806,7 @@
         <v>26</v>
       </c>
       <c r="Q81" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="R81" t="s">
         <v>32</v>
@@ -6809,16 +6818,16 @@
         <v>74.18179719</v>
       </c>
       <c r="U81" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="V81">
         <v>1314.5</v>
       </c>
       <c r="W81" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="X81" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="82" spans="1:24">
@@ -6871,7 +6880,7 @@
         <v>26</v>
       </c>
       <c r="Q82" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="R82" t="s">
         <v>32</v>
@@ -6883,16 +6892,16 @@
         <v>74.18230296</v>
       </c>
       <c r="U82" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="V82">
         <v>52394.5</v>
       </c>
       <c r="W82" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="X82" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="83" spans="1:24">
@@ -6945,7 +6954,7 @@
         <v>26</v>
       </c>
       <c r="Q83" t="s">
-        <v>27</v>
+        <v>88</v>
       </c>
       <c r="R83" t="s">
         <v>32</v>
@@ -6957,16 +6966,16 @@
         <v>74.46541999999999</v>
       </c>
       <c r="U83" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="V83">
         <v>150000</v>
       </c>
       <c r="W83" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="X83" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="84" spans="1:24">
@@ -7019,7 +7028,7 @@
         <v>26</v>
       </c>
       <c r="Q84" t="s">
-        <v>27</v>
+        <v>88</v>
       </c>
       <c r="R84" t="s">
         <v>32</v>
@@ -7031,16 +7040,16 @@
         <v>74.46541999999999</v>
       </c>
       <c r="U84" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="V84">
         <v>150000</v>
       </c>
       <c r="W84" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="X84" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
   </sheetData>
